--- a/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_True.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,10 +668,10 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301524983055982</v>
+        <v>0.231221769167109</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1989795524883176</v>
+        <v>0.2007211518461947</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.423003083472088</v>
       </c>
       <c r="P2" t="n">
-        <v>4.388872515132739</v>
+        <v>4.425560250819469</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9916770644418813</v>
+        <v>0.9918567268035426</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005607919145620375</v>
+        <v>0.0055470614871942</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9877895547140725</v>
+        <v>0.98869250484893</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.008013417116864322</v>
+        <v>0.007711435021981065</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9996119866029118</v>
+        <v>0.9996179105578975</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001296103710073375</v>
+        <v>0.0001286171589219084</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9967957613449662</v>
+        <v>0.9966850795360935</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002388398569125294</v>
+        <v>0.002429298774071136</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9589292538283284</v>
+        <v>0.9581644567964351</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008623533981904472</v>
+        <v>0.008703455009517067</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7277900929539205</v>
+        <v>0.7279095922182931</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001570040600762434</v>
+        <v>0.001569695941572063</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -772,10 +772,10 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1224260723227339</v>
+        <v>0.1221977047489524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1438169141066449</v>
+        <v>0.1443142982267897</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.306107642639816</v>
       </c>
       <c r="P3" t="n">
-        <v>4.323195470239729</v>
+        <v>4.33746382545987</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9890020805393449</v>
+        <v>0.9889990008559164</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006377126570042053</v>
+        <v>0.006378019382377876</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9921150871353288</v>
+        <v>0.9922047187864307</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005705924108476546</v>
+        <v>0.005673400404644776</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.9997607700458169</v>
+        <v>0.9997436944936144</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.787490678985068e-05</v>
+        <v>3.920331231647279e-05</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9724880046871851</v>
+        <v>0.972430530330863</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.008044665820353705</v>
+        <v>0.008053064352710118</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8614283115085157</v>
+        <v>0.8609634914468878</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009027910914438433</v>
+        <v>0.009043039693689204</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3389812411836787</v>
+        <v>0.3381051712068962</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003317295903387125</v>
+        <v>0.003319493436383504</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -876,10 +876,10 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3654424073581523</v>
+        <v>0.3697996722445903</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2372284706730699</v>
+        <v>0.2434823022440334</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.407250937879116</v>
       </c>
       <c r="P4" t="n">
-        <v>4.445380278326204</v>
+        <v>4.484256662032916</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9497355932643246</v>
+        <v>0.952126288759651</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01466609013777161</v>
+        <v>0.0143130641352328</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9760563581560929</v>
+        <v>0.9822948653116685</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01362488057292417</v>
+        <v>0.01171621190359204</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9367276456261356</v>
+        <v>0.9541461425661923</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.003130509369219023</v>
+        <v>0.002664992239114771</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.2715444681321789</v>
+        <v>0.271675611020961</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02777850830735695</v>
+        <v>0.02777600773069858</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9867167499805214</v>
+        <v>0.9854820987101983</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004780628750624676</v>
+        <v>0.004997867808762986</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.3340292071408895</v>
+        <v>0.3169282047793512</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004135484824818648</v>
+        <v>0.004188244401585439</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -980,10 +980,10 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851828485504524</v>
+        <v>0.1827280879260966</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2201364392277761</v>
+        <v>0.2173629647558321</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.284288814452183</v>
       </c>
       <c r="P5" t="n">
-        <v>4.405449187243251</v>
+        <v>4.352672707714889</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9961812443712929</v>
+        <v>0.9961863812255521</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003657620760223519</v>
+        <v>0.003655159881691033</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9950525078481989</v>
+        <v>0.9950768263004883</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005038023504033622</v>
+        <v>0.00502562653060317</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999998997906608</v>
+        <v>0.9999999303532935</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.950784141299889e-06</v>
+        <v>1.626317777467947e-06</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9965816771365754</v>
+        <v>0.996570261593108</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002717820808418715</v>
+        <v>0.002722355128832427</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9738024152371193</v>
+        <v>0.9737911724939311</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005381508968666206</v>
+        <v>0.005382663587193134</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9676770489959852</v>
+        <v>0.9675076390776964</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008382598018959948</v>
+        <v>0.0008404536600112487</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1084,10 +1084,10 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1720532088902192</v>
+        <v>0.1686949453492942</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2065587519000903</v>
+        <v>0.2032196895738114</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.342240366865149</v>
       </c>
       <c r="P6" t="n">
-        <v>4.472248625751038</v>
+        <v>4.389808818884189</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9747704020460646</v>
+        <v>0.9748594133187256</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009602084920852476</v>
+        <v>0.009585131638762059</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9802733552065045</v>
+        <v>0.9806330858151963</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008101582249882758</v>
+        <v>0.008027373072053283</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9997489681049959</v>
+        <v>0.9997436850972771</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.23171314407404e-05</v>
+        <v>4.276009850895156e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9874802954847093</v>
+        <v>0.9878096976082793</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004589237462271792</v>
+        <v>0.004528462023650734</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6775349362051399</v>
+        <v>0.6773249744471392</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01844829680808588</v>
+        <v>0.01845430180980078</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4184358316533658</v>
+        <v>0.416379044741942</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001797009964223077</v>
+        <v>0.001800184854132759</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1188,10 +1188,10 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1710817277651676</v>
+        <v>0.1697000243333415</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1645839601838462</v>
+        <v>0.1648970046130869</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.332467324133582</v>
       </c>
       <c r="P7" t="n">
-        <v>4.319167924868395</v>
+        <v>4.35956137579332</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9860586651546587</v>
+        <v>0.9859943408612178</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007174027794666943</v>
+        <v>0.007190558966467463</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9844525095205374</v>
+        <v>0.9842741824144735</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009460445438480257</v>
+        <v>0.00951454561139514</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9828921198120371</v>
+        <v>0.9859438385817348</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0005642935081450484</v>
+        <v>0.0005114937388193356</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9193748174143648</v>
+        <v>0.9193479855511263</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01131958982913299</v>
+        <v>0.01132147323832901</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9964526965898581</v>
+        <v>0.9963504404849115</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001568385046339256</v>
+        <v>0.001590829917537565</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.2869782311665148</v>
+        <v>0.2867654836834522</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004457864679826117</v>
+        <v>0.004458529686701029</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1292,10 +1292,10 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1467886062531126</v>
+        <v>0.1487814895648295</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1586415142560278</v>
+        <v>0.1643432844717302</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.46691264392827</v>
       </c>
       <c r="P8" t="n">
-        <v>4.283630287819499</v>
+        <v>4.408244358875646</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9918625760503544</v>
+        <v>0.9919380527634488</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004859721100519864</v>
+        <v>0.004837131010806054</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9897651798778276</v>
+        <v>0.9898702488707458</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.006750652312946607</v>
+        <v>0.006715912376889003</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9998825638533526</v>
+        <v>0.9998830110199964</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.113084917954816e-05</v>
+        <v>7.099529602858357e-05</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9860329161642536</v>
+        <v>0.9860347330505472</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005852095429657281</v>
+        <v>0.005851714786929574</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.983051639701812</v>
+        <v>0.9833584222668272</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.00551246465997629</v>
+        <v>0.005462346216131495</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9997615199878828</v>
+        <v>0.9997548019790157</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.641118547004214e-05</v>
+        <v>5.720022198237029e-05</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1396,10 +1396,10 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1635011120245474</v>
+        <v>0.1638384053732252</v>
       </c>
       <c r="L9" t="n">
-        <v>0.162164971487591</v>
+        <v>0.1616259254391911</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.269965407827312</v>
       </c>
       <c r="P9" t="n">
-        <v>4.388029705565765</v>
+        <v>4.356424141651297</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.993369910117495</v>
+        <v>0.9933836391401224</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004403737004355446</v>
+        <v>0.004399175200757764</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9901450455724291</v>
+        <v>0.9902465280863846</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007165421305502604</v>
+        <v>0.007128432464503286</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9996043283571675</v>
+        <v>0.9995420389415455</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001139187616917894</v>
+        <v>0.0001225581135728245</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9997794376914381</v>
+        <v>0.999776735421138</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006009435422655711</v>
+        <v>0.0006046136348618595</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9731496266616629</v>
+        <v>0.9729178945644251</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00618268143698178</v>
+        <v>0.006209303929374495</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9844644290803072</v>
+        <v>0.9843089361077836</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007494005044613266</v>
+        <v>0.0007531414802217934</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1500,10 +1500,10 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.204060541149278</v>
+        <v>0.2045760244746017</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1167264402311615</v>
+        <v>0.1179390585897766</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.174498702949626</v>
       </c>
       <c r="P10" t="n">
-        <v>4.178693952756554</v>
+        <v>4.218389167765724</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9859560132291421</v>
+        <v>0.9859838478021674</v>
       </c>
       <c r="R10" t="n">
-        <v>0.007527928990114295</v>
+        <v>0.007520465275615061</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.98791935839433</v>
+        <v>0.987979616375028</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00972201052203516</v>
+        <v>0.009697733621253734</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9998730843742911</v>
+        <v>0.9999226822629682</v>
       </c>
       <c r="AD10" t="n">
-        <v>9.416326915863348e-05</v>
+        <v>7.349597362621352e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9081102662615413</v>
+        <v>0.9081271632801182</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01239488149375979</v>
+        <v>0.01239374183341249</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9660126773370766</v>
+        <v>0.9660960378853024</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002916807803220991</v>
+        <v>0.002913228586725021</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7924252682453615</v>
+        <v>0.7924590047267251</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002791847900155101</v>
+        <v>0.002791621015718941</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1604,10 +1604,10 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1486625876472495</v>
+        <v>0.149201674972049</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3040134679347565</v>
+        <v>0.3042608521164594</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.076850431013222</v>
       </c>
       <c r="P11" t="n">
-        <v>4.252041912262387</v>
+        <v>4.249525989654821</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9928125935444038</v>
+        <v>0.9927342809764135</v>
       </c>
       <c r="R11" t="n">
-        <v>0.006307070055404485</v>
+        <v>0.00634133726390207</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9894265039432576</v>
+        <v>0.9892903729241561</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01285641383607196</v>
+        <v>0.0129389106506787</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9790180383263885</v>
+        <v>0.9794387791119039</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001020280873797122</v>
+        <v>0.001009999479786321</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9594339945235666</v>
+        <v>0.9595744122075853</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003570261138621759</v>
+        <v>0.003564076620590171</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9497339571640988</v>
+        <v>0.9500994871820255</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002519361103242637</v>
+        <v>0.002510184108685442</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.968760527211004</v>
+        <v>0.9688265348984452</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0007487648446086101</v>
+        <v>0.000747973372044176</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1708,10 +1708,10 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09817290404296372</v>
+        <v>0.09975764557508192</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1718435081487066</v>
+        <v>0.1656875470041076</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.05812402486322</v>
       </c>
       <c r="P12" t="n">
-        <v>4.067921896405536</v>
+        <v>4.120997695165938</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9443244677351456</v>
+        <v>0.945533999647139</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02567996912426333</v>
+        <v>0.02539949317205216</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.6884050910475417</v>
+        <v>0.6935125424392137</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05517852399746583</v>
+        <v>0.0547244311336627</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9782951455975354</v>
+        <v>0.9871473859788719</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0003459788209947356</v>
+        <v>0.0002662360177207508</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9866230733014628</v>
+        <v>0.9986764530665788</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.004373425372869361</v>
+        <v>0.001375666684079948</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.2813288824807386</v>
+        <v>0.2648964248668589</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.003683154897017043</v>
+        <v>0.003725024688202526</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9897343030718124</v>
+        <v>0.9883604535002856</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002049604476650598</v>
+        <v>0.0002182447832766946</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1812,10 +1812,10 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1114576132023562</v>
+        <v>0.1219723482576723</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1918612233468548</v>
+        <v>0.2090384686883623</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.289380695969488</v>
       </c>
       <c r="P13" t="n">
-        <v>4.288069972053308</v>
+        <v>4.509167032838435</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9975486737181489</v>
+        <v>0.9975489251894432</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002833304730455287</v>
+        <v>0.002833159398296388</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.7873261472398192</v>
+        <v>0.7859972271476799</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003635949233023157</v>
+        <v>0.003647291392042863</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9934627372234783</v>
+        <v>0.9984871601511938</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.191972372649307e-05</v>
+        <v>2.978705150908228e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.5720261016220962</v>
+        <v>0.572831286104469</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004678110691146722</v>
+        <v>0.004673707951291557</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.99999480279391</v>
+        <v>0.9999881277817543</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.210195439966931e-05</v>
+        <v>0.0001392033902400646</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.951263725001637</v>
+        <v>0.9517830277239331</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002240739876060582</v>
+        <v>0.002228769955838406</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1916,10 +1916,10 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1914146643757773</v>
+        <v>0.1913164990551056</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3041874353183426</v>
+        <v>0.2977137660328253</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.361494374090167</v>
       </c>
       <c r="P14" t="n">
-        <v>4.327932271653679</v>
+        <v>4.373232155389765</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9793412325693427</v>
+        <v>0.9799160865309536</v>
       </c>
       <c r="R14" t="n">
-        <v>0.008559479857663886</v>
+        <v>0.008439550996821529</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9456199190101637</v>
+        <v>0.9520278104195266</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01159453532346044</v>
+        <v>0.01089000787048949</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.8114166659292152</v>
+        <v>0.8287003913264104</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.002129699070763514</v>
+        <v>0.00202976038465065</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9972374641596256</v>
+        <v>0.9933409845184025</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.00227155294107149</v>
+        <v>0.003526743825810193</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.5710481342289888</v>
+        <v>0.5734291701102299</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01479989118118372</v>
+        <v>0.01475875823316106</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.1898236981574882</v>
+        <v>0.1895255856938327</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001777041904631331</v>
+        <v>0.001777368814722072</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2020,10 +2020,10 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1960420645582539</v>
+        <v>0.18717447583358</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2852465007238459</v>
+        <v>0.2802587248821268</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.078910665279218</v>
       </c>
       <c r="P15" t="n">
-        <v>4.33049142742116</v>
+        <v>4.254817618534121</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9789543988063977</v>
+        <v>0.978939470265888</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007666626392674872</v>
+        <v>0.007669345042821305</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9522609945055583</v>
+        <v>0.9523521479509817</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01075875153459288</v>
+        <v>0.01074847518041454</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.07861826633393743</v>
+        <v>-0.05221748830324335</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.002717651560148048</v>
+        <v>0.002684186241680081</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9206719983118964</v>
+        <v>0.920673876493834</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0103132800586745</v>
+        <v>0.01031315796855143</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.6423855816089263</v>
+        <v>0.6376043548420356</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.006692779980758107</v>
+        <v>0.006737371933681222</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999999505931797</v>
+        <v>0.9999999861731875</v>
       </c>
       <c r="AM15" t="n">
-        <v>8.225319123553672e-07</v>
+        <v>4.351313172522935e-07</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5421174973423735</v>
+        <v>0.5236690839066376</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5486489695491799</v>
+        <v>0.5447407781101302</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.405739545165345</v>
       </c>
       <c r="P16" t="n">
-        <v>4.642265550007799</v>
+        <v>4.587988865286516</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9756614818213272</v>
+        <v>0.9764932249988238</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009488759899409638</v>
+        <v>0.009325216342966111</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9941472657617892</v>
+        <v>0.9942086516286338</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005639539971318783</v>
+        <v>0.005609887114394181</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9581923875116397</v>
+        <v>0.9601817919991722</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004214255924509277</v>
+        <v>0.004112766733193757</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9106241229170851</v>
+        <v>0.9084533900052759</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003589626771776325</v>
+        <v>0.003632957109193859</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8403926380289104</v>
+        <v>0.8464648288755372</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01810272524818962</v>
+        <v>0.01775503116466925</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2226,10 +2226,10 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1718661769237949</v>
+        <v>0.1754337283424276</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2645200185348528</v>
+        <v>0.2580489919528897</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.87520233994104</v>
       </c>
       <c r="P17" t="n">
-        <v>4.201007384925188</v>
+        <v>4.032109036058404</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9922918278369821</v>
+        <v>0.9920879992474081</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004075423509922515</v>
+        <v>0.004128955510096162</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9806637131644284</v>
+        <v>0.9799998131293119</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.00699550156099667</v>
+        <v>0.007114581269888968</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.686173054481225</v>
+        <v>0.7280412325566102</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001732573495462018</v>
+        <v>0.001612865244953714</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9936316392375492</v>
+        <v>0.9935022091777753</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.00215818937948075</v>
+        <v>0.002180010499502885</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.02035165774484016</v>
+        <v>-0.009983428235382341</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005093530966193179</v>
+        <v>0.005171791056765838</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.994605716700115</v>
+        <v>0.9944111180408979</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.000710416650838848</v>
+        <v>0.0007231172551854027</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2393672981629223</v>
+        <v>0.2418615173003435</v>
       </c>
       <c r="L18" t="n">
-        <v>0.264637894152249</v>
+        <v>0.2681713861606304</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.288454172770764</v>
       </c>
       <c r="P18" t="n">
-        <v>4.251167394404778</v>
+        <v>4.303901155160221</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9849947172351137</v>
+        <v>0.985026502892796</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006335205031648485</v>
+        <v>0.006328491548989255</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9272626768070292</v>
+        <v>0.9274006724570588</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01385004501482206</v>
+        <v>0.01383690077720659</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9989286803176163</v>
+        <v>0.9988944085935337</v>
       </c>
       <c r="AD18" t="n">
-        <v>9.015040938163686e-05</v>
+        <v>9.158102257762326e-05</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9975918188107467</v>
+        <v>0.9975720017418588</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001472909204829176</v>
+        <v>0.001478957117696714</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9766587551550604</v>
+        <v>0.9769438024956949</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002570229163965521</v>
+        <v>0.002554486911816233</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.995305997173703</v>
+        <v>0.9952075988858086</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002582643514749129</v>
+        <v>0.000260957252360046</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2434,10 +2434,10 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1872651872905624</v>
+        <v>0.1612348717429317</v>
       </c>
       <c r="L19" t="n">
-        <v>0.241782904144955</v>
+        <v>0.2283845797447064</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.597747250805167</v>
+        <v>3.995533644292064</v>
       </c>
       <c r="P19" t="n">
-        <v>4.658165486387739</v>
+        <v>4.383591224703615</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9875090719397286</v>
+        <v>0.9875825126842892</v>
       </c>
       <c r="R19" t="n">
-        <v>0.007874473081973895</v>
+        <v>0.007851289867939881</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.7072848516592726</v>
+        <v>0.710156516457392</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.008055802217546542</v>
+        <v>0.008016189335489678</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>0.1568347211629071</v>
+        <v>0.174744410865898</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.002735668172065737</v>
+        <v>0.002706458036445235</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7270137332522709</v>
+        <v>0.7274633092627021</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01474686946725469</v>
+        <v>0.01473472129088299</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8485647325587395</v>
+        <v>0.8536031969239449</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004489584417278173</v>
+        <v>0.004414265229393905</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9964582563602615</v>
+        <v>0.9962789382458113</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001739958438018418</v>
+        <v>0.0001783461555048031</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2538,10 +2538,10 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2655681489740055</v>
+        <v>0.2693988039088081</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2942662670007738</v>
+        <v>0.2995141343496358</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.607232881973829</v>
       </c>
       <c r="P20" t="n">
-        <v>4.51180200867902</v>
+        <v>4.593845696015604</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9764466235552127</v>
+        <v>0.9762962510084028</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009010238613638002</v>
+        <v>0.009038955024765819</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8987313606460009</v>
+        <v>0.8968608003763588</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.009270559544244154</v>
+        <v>0.009355787278112298</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8343190716350202</v>
+        <v>0.8330609224095268</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002777441886080602</v>
+        <v>0.002787967622029889</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.957772705517727</v>
+        <v>0.9570038691571811</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.005483419822247009</v>
+        <v>0.005533113222151439</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7910929431610494</v>
+        <v>0.7908000271674109</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01678453064928702</v>
+        <v>0.01679629362026933</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4677335975270138</v>
+        <v>0.4643581990916192</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006900576901016203</v>
+        <v>0.0006922422527367349</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1248690725745343</v>
+        <v>0.120044065289244</v>
       </c>
       <c r="L21" t="n">
-        <v>0.136174727105988</v>
+        <v>0.1354346365046291</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.099687029519429</v>
       </c>
       <c r="P21" t="n">
-        <v>4.342615063521492</v>
+        <v>4.124831078561143</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.876610304573435</v>
+        <v>0.8659344877616386</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02286020641684946</v>
+        <v>0.02382863897532373</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9272278868680222</v>
+        <v>0.9306633375099265</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01059669116751348</v>
+        <v>0.01034354125347507</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9977315518408773</v>
+        <v>0.9974187279747142</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.001572175015329854</v>
+        <v>0.001677078333553553</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.404946634328127</v>
+        <v>-3.879834502240177</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04597049071818667</v>
+        <v>0.04838506855308401</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.3236827374681548</v>
+        <v>-0.3346792842067901</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01960603125856781</v>
+        <v>0.01968730175858778</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.5318322874152435</v>
+        <v>0.5197619066445416</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0007078916184804008</v>
+        <v>0.0007169590379083107</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2746,10 +2746,10 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.281180272555923</v>
+        <v>0.2811593684201072</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3250602831602623</v>
+        <v>0.321775101569801</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.136621870834812</v>
       </c>
       <c r="P22" t="n">
-        <v>4.394904526854336</v>
+        <v>4.310076641693127</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.982042673445116</v>
+        <v>0.9820647239956858</v>
       </c>
       <c r="R22" t="n">
-        <v>0.00677402467042048</v>
+        <v>0.006769864339093113</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8976092540679207</v>
+        <v>0.8978847682687321</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.00943364369950386</v>
+        <v>0.00942094307133092</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9276440265773008</v>
+        <v>0.9298081422905806</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.00149092906965972</v>
+        <v>0.001468463497998433</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3411466417297978</v>
+        <v>0.3418109742691106</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01120342122382867</v>
+        <v>0.01119777150352522</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.957199953575134</v>
+        <v>0.956446695636878</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002962297472478973</v>
+        <v>0.002988251203598708</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7802090128142136</v>
+        <v>0.7804140096473513</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001982093540525068</v>
+        <v>0.001981168985584216</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2118075530290184</v>
+        <v>0.2096861360727826</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2785599610829989</v>
+        <v>0.2752406104882666</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.857921490702031</v>
       </c>
       <c r="P23" t="n">
-        <v>4.196068842471415</v>
+        <v>4.107349822216892</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9810092156458454</v>
+        <v>0.9810167656443608</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01031715618691274</v>
+        <v>0.01031510513267665</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8929483276489992</v>
+        <v>0.8929865752045899</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02293770345700766</v>
+        <v>0.02293360548523138</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.6934768711185186</v>
+        <v>-0.6467037899344668</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001242723685241882</v>
+        <v>0.001225441781162331</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9850655941228458</v>
+        <v>0.9851183846284315</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002058328265262757</v>
+        <v>0.002054687130006122</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.892352842898134</v>
+        <v>0.8793314987716929</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0005326833751068619</v>
+        <v>0.000563981449851673</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.999286331763955</v>
+        <v>0.9993002898881095</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001244590719145468</v>
+        <v>0.0001232359591140869</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2954,10 +2954,10 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3715559515835667</v>
+        <v>0.3822690760043342</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4403187307337946</v>
+        <v>0.4469060831203862</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.250849247723202</v>
       </c>
       <c r="P24" t="n">
-        <v>4.308862456439905</v>
+        <v>4.315438599653929</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9923744879839038</v>
+        <v>0.9923262185718489</v>
       </c>
       <c r="R24" t="n">
-        <v>0.005185864292536362</v>
+        <v>0.00520225163414097</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9991976144011084</v>
+        <v>0.9991068166061686</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.002273076911420975</v>
+        <v>0.002398241356930686</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9413794707932834</v>
+        <v>0.9382511292855351</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.00382273119909852</v>
+        <v>0.003923407368471433</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8408897619494797</v>
+        <v>0.8421435473736182</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009830090076950581</v>
+        <v>0.009791283021592425</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.997232555149305</v>
+        <v>0.994284036697847</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0003554245478165205</v>
+        <v>0.0005108020693029962</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2172140991091026</v>
+        <v>0.2154668003430986</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2295163109220416</v>
+        <v>0.2294009511087869</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.303014593509248</v>
       </c>
       <c r="P25" t="n">
-        <v>4.344403145138528</v>
+        <v>4.342456320621022</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9848721561371977</v>
+        <v>0.984922041146198</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02039822636914438</v>
+        <v>0.02036456638518282</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1474332522190893</v>
+        <v>-0.1434164159467208</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03943817310172244</v>
+        <v>0.03936908168833141</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5354915722554054</v>
+        <v>0.5380471058984511</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008647945192577816</v>
+        <v>0.0008624123670844852</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8976486003966551</v>
+        <v>0.8975779533860648</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01102899160011401</v>
+        <v>0.01103279726805333</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.6541954691243346</v>
+        <v>0.654847948708293</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002881795694758269</v>
+        <v>0.002879075660041329</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.970493465028674</v>
+        <v>0.9699181221291553</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002813829766617591</v>
+        <v>0.002841130519595289</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.978441683362923</v>
+        <v>0.9748671958439692</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0009170710637411286</v>
+        <v>0.0009901843108232609</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02357855703402167</v>
+        <v>-0.02271122221175204</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003350208631183936</v>
+        <v>0.003348788921675589</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3168,10 +3168,10 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3294247814180385</v>
+        <v>0.3206536186429215</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3219835329484267</v>
+        <v>0.3143837239406004</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.234787854458681</v>
       </c>
       <c r="P26" t="n">
-        <v>4.388090915242517</v>
+        <v>4.297137267092482</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9804511550933579</v>
+        <v>0.9805752566094734</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02149056723706279</v>
+        <v>0.02142224457626787</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.2872614361236882</v>
+        <v>0.2919906370964104</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04145897644591403</v>
+        <v>0.04132120211662515</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3421231294616038</v>
+        <v>-0.3275677251190763</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008121310865625367</v>
+        <v>0.0008077152767758603</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9473222060047918</v>
+        <v>0.9471432283199523</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01239128549513487</v>
+        <v>0.01241231791554477</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.2595749855777725</v>
+        <v>-0.2504148276689557</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003848183652329285</v>
+        <v>0.003834165315760165</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9025750534290341</v>
+        <v>0.9040329216646996</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.004178000271872033</v>
+        <v>0.004146622618851097</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9972103087783235</v>
+        <v>0.9975319164238524</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.0004493016302558082</v>
+        <v>0.0004226100857984786</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4621114049431704</v>
+        <v>0.4587902950732933</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001016285872374794</v>
+        <v>0.001019418494247144</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3280,10 +3280,10 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2426473726089903</v>
+        <v>0.2430405588533768</v>
       </c>
       <c r="L27" t="n">
-        <v>0.305733301008045</v>
+        <v>0.3051947099590636</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.135167174011909</v>
       </c>
       <c r="P27" t="n">
-        <v>4.157145868084897</v>
+        <v>4.152397114719814</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9961668014285981</v>
+        <v>0.9961713086661211</v>
       </c>
       <c r="R27" t="n">
-        <v>0.01004867487444007</v>
+        <v>0.01004276530760784</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.8974051860180551</v>
+        <v>0.8975561274551627</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01681450315066318</v>
+        <v>0.01680212952590892</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.7050963090556052</v>
+        <v>0.70391716480052</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006085721759822495</v>
+        <v>0.0006097876211079581</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9092419503987114</v>
+        <v>0.9093238988441408</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01277473935160243</v>
+        <v>0.01276897068174134</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9419899204116621</v>
+        <v>0.9416527866436839</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0008807453056330979</v>
+        <v>0.0008833008858315042</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8853186686225081</v>
+        <v>0.8852490554518301</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009460139969545365</v>
+        <v>0.009463010752537832</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.612199841903271</v>
+        <v>0.6135405126304565</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003354976821617136</v>
+        <v>0.003349172526138858</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4393452776827648</v>
+        <v>0.4392080963373839</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.0048754306403539</v>
+        <v>0.004876027065570017</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3392,10 +3392,10 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4028027310904022</v>
+        <v>0.3989682187359773</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3951444476402755</v>
+        <v>0.4092044112436037</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.115059320054375</v>
       </c>
       <c r="P28" t="n">
-        <v>4.168679494166031</v>
+        <v>4.291920661630636</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9429208267296751</v>
+        <v>0.9444724491243617</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02487954835729252</v>
+        <v>0.02453905954847143</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6043823958124592</v>
+        <v>0.6168139696338479</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05153925842985136</v>
+        <v>0.05072303073723201</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.8250244870587615</v>
+        <v>0.8455350749967376</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.005002944450409662</v>
+        <v>0.004700585775864934</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5067283168913198</v>
+        <v>0.5039501493547531</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01174055289482331</v>
+        <v>0.01177356860081368</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4029621236478237</v>
+        <v>0.4013347893632664</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01679043465182906</v>
+        <v>0.01681330175749516</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9888942832426164</v>
+        <v>0.9895115398216148</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003648353894288969</v>
+        <v>0.0003545516649194897</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3498,10 +3498,10 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.512131704883432</v>
+        <v>0.5374259014890495</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3484594399827672</v>
+        <v>0.3599059019324887</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.282902876970244</v>
       </c>
       <c r="P29" t="n">
-        <v>4.100422258910463</v>
+        <v>4.206241362661623</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9364647560613805</v>
+        <v>0.9366852314083038</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01626579965253213</v>
+        <v>0.01623755293340796</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7241430225019209</v>
+        <v>0.7220543066191655</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03422580193551732</v>
+        <v>0.03435513193226034</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9100225380611278</v>
+        <v>0.9118205146818732</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.01038977193014634</v>
+        <v>0.01028544117865461</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.5180882309150002</v>
+        <v>0.5783721282856094</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.009811883170696471</v>
+        <v>0.009177687338251372</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9848363155942869</v>
+        <v>0.9841052831601101</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.003199552830876101</v>
+        <v>0.003275769347948588</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9112177205651673</v>
+        <v>0.9107411282913163</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001778252710659725</v>
+        <v>0.001783019242800507</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3604,10 +3604,10 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4480149274440504</v>
+        <v>0.4720730841162494</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3847343291561345</v>
+        <v>0.405421165090822</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.562326845844513</v>
       </c>
       <c r="P30" t="n">
-        <v>4.108425083456869</v>
+        <v>4.311808835799374</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9742984157201915</v>
+        <v>0.974574664470278</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01321435093067845</v>
+        <v>0.01314314306267128</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8799960049673983</v>
+        <v>0.8803853003666599</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02359618552995083</v>
+        <v>0.02355788118694438</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9936560983873693</v>
+        <v>0.9774394151432966</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0003589307051383038</v>
+        <v>0.0006768735906511553</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>-0.1036688600231264</v>
+        <v>-0.0598327692119871</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01420731058316668</v>
+        <v>0.01392230525653433</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8472076223739231</v>
+        <v>0.8455198730648406</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008181351530277922</v>
+        <v>0.008226413164469575</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4726982510477971</v>
+        <v>0.4721200216573848</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.00195294928451405</v>
+        <v>0.001954019775240407</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3710,10 +3710,10 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5036033975236921</v>
+        <v>0.4939662194456111</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4314681902681919</v>
+        <v>0.4302221753435271</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.280086717342922</v>
       </c>
       <c r="P31" t="n">
-        <v>4.40046806268827</v>
+        <v>4.391843893111419</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9842490341788166</v>
+        <v>0.9843425949262706</v>
       </c>
       <c r="R31" t="n">
-        <v>0.008196155908287492</v>
+        <v>0.008171777066008253</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9340382043011461</v>
+        <v>0.9354362236608754</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01371776715105505</v>
+        <v>0.01357161883866285</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.9160807446662944</v>
+        <v>0.9153744453987112</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007052646644950027</v>
+        <v>0.007082263458684884</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.06580910632191372</v>
+        <v>-0.08004122772935918</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009387168042783002</v>
+        <v>0.009449635265128218</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9792999345711391</v>
+        <v>0.9776912208910113</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002257644946447069</v>
+        <v>0.002343730572965135</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.02711781354510545</v>
+        <v>0.02109647890011457</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004145717026360672</v>
+        <v>0.004158526513618752</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3816,10 +3816,10 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4586807473470598</v>
+        <v>0.5041910255103661</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3971533783108466</v>
+        <v>0.4272514680364557</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.563241224115946</v>
       </c>
       <c r="P32" t="n">
-        <v>4.108143889101155</v>
+        <v>4.417668249325046</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9795655394133629</v>
+        <v>0.9801322792381413</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0137649784282196</v>
+        <v>0.0135727537514664</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.9031879130685662</v>
+        <v>0.9186604828168569</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.008874018343056138</v>
+        <v>0.008134040418942189</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2236914916151639</v>
+        <v>0.2235580084396153</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01748939141771184</v>
+        <v>0.01749089496889964</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.6652605144848913</v>
+        <v>-0.5553005073651391</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01641092574504382</v>
+        <v>0.01585985253824754</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2614802910412648</v>
+        <v>0.2554367786861873</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01780623578462693</v>
+        <v>0.01787894403175592</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.08135890080624975</v>
+        <v>0.07620075321996744</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004871784384308527</v>
+        <v>0.004885442714179641</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3920,10 +3920,10 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2751054178962024</v>
+        <v>0.2828125477845588</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2826924042382675</v>
+        <v>0.2943407216269099</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.275571175206728</v>
       </c>
       <c r="P33" t="n">
-        <v>4.151168606367992</v>
+        <v>4.266016694531364</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.964575762437468</v>
+        <v>0.9643692358022204</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005971056185663683</v>
+        <v>0.005988436799279399</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9261550082803731</v>
+        <v>0.9254577824922631</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01098091608323249</v>
+        <v>0.01103263381372728</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.08132796054716229</v>
+        <v>0.09788660787930459</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006150937384786307</v>
+        <v>0.006095251385106984</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.9026100004524901</v>
+        <v>0.8974986867492309</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.003722415044184477</v>
+        <v>0.003818847603978114</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7610737867492676</v>
+        <v>0.7673254880507041</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002319338417123484</v>
+        <v>0.002288793584340332</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3685057893410572</v>
+        <v>0.3722924463802223</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007856886590063022</v>
+        <v>0.0007833294870260849</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4024,10 +4024,10 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5165578838213738</v>
+        <v>0.5387040856238987</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4281011815156123</v>
+        <v>0.4505244806061678</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.291280449636701</v>
       </c>
       <c r="P34" t="n">
-        <v>4.124458637938648</v>
+        <v>4.281402786162578</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8727855984803289</v>
+        <v>0.8632025530430495</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02487254662126047</v>
+        <v>0.02579236167805296</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.7913242023823326</v>
+        <v>0.7748859956775074</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.05468492546313623</v>
+        <v>0.05679797340671861</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9942236221078945</v>
+        <v>0.9938226148081223</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001797845492425776</v>
+        <v>0.001859203414570875</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.5636145298774535</v>
+        <v>0.5878152494809181</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.005085552430598888</v>
+        <v>0.004942525917212037</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4016337360454056</v>
+        <v>0.4122539526376154</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.008586634025604657</v>
+        <v>0.00851009212803502</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.196332054581197</v>
+        <v>0.1776844239965625</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0008714875214799828</v>
+        <v>0.0008815401718817203</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4130,10 +4130,10 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3001566209783726</v>
+        <v>0.3025718444011018</v>
       </c>
       <c r="L35" t="n">
-        <v>0.241519443022537</v>
+        <v>0.2499379673751634</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.05737490915139</v>
       </c>
       <c r="P35" t="n">
-        <v>4.0279033465417</v>
+        <v>4.15103321646585</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9970029285559046</v>
+        <v>0.9970166090418883</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005453841723835828</v>
+        <v>0.005441380135174591</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9896717136829084</v>
+        <v>0.9897875062409014</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.005545728157551768</v>
+        <v>0.005514553380805504</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6177738463458643</v>
+        <v>0.6186558180004975</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.009233024728050753</v>
+        <v>0.009222366157186327</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7107400993257729</v>
+        <v>0.7113312356780586</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002173431147773197</v>
+        <v>0.002171209181928795</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5067979141164942</v>
+        <v>0.5090415643156302</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002384534797691882</v>
+        <v>0.002379104812129503</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4232,10 +4232,10 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4200622561347667</v>
+        <v>0.432114221689511</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3831470969423511</v>
+        <v>0.393460572400415</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.321952334671811</v>
       </c>
       <c r="P36" t="n">
-        <v>4.208116985919483</v>
+        <v>4.315683993496754</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9838311506301053</v>
+        <v>0.9838277884668162</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01152230180676141</v>
+        <v>0.01152349972275295</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8140484756149892</v>
+        <v>0.8138287247343752</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.0187452514919585</v>
+        <v>0.01875632445640098</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.399263116702305</v>
+        <v>0.4013374024056481</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.00795086873476508</v>
+        <v>0.007937130078895365</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06329419011179849</v>
+        <v>0.06460173304454087</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01350317084775786</v>
+        <v>0.0134937430523918</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7300264817381893</v>
+        <v>0.7286972638153408</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006087052845881462</v>
+        <v>0.006102019286247539</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1516923509561995</v>
+        <v>0.1549866676212358</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004072969577069452</v>
+        <v>0.004065053402173327</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4338,10 +4338,10 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1057540787127461</v>
+        <v>0.1035375728459106</v>
       </c>
       <c r="L37" t="n">
-        <v>0.120064366324867</v>
+        <v>0.117180601009066</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.240813110988225</v>
       </c>
       <c r="P37" t="n">
-        <v>4.361018274195376</v>
+        <v>4.271075171498469</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9931644223093784</v>
+        <v>0.9931872717709982</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005509045775834268</v>
+        <v>0.005499830453704712</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.04793761294103449</v>
+        <v>0.05207706353987218</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004174275264766007</v>
+        <v>0.0004165190760751575</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9959748082314557</v>
+        <v>0.9961141164805039</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.003012194123738487</v>
+        <v>0.002959610491539008</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.4726764567523976</v>
+        <v>-0.4729812322212641</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007683644900095252</v>
+        <v>0.0076844399373618</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9166449031496721</v>
+        <v>0.916852348976366</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009395451424115039</v>
+        <v>0.009383752911239048</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9333841627849404</v>
+        <v>0.9336211192272117</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.00231561453480265</v>
+        <v>0.002311492477542115</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999986044701493</v>
+        <v>0.9999993425584421</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.162854318042043e-06</v>
+        <v>7.981496381906415e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1483762115382365</v>
+        <v>0.1433109613706779</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1328653447106774</v>
+        <v>0.1277653508763556</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.158873949626578</v>
       </c>
       <c r="P38" t="n">
-        <v>4.345534482782154</v>
+        <v>4.198981036502904</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9432714659421326</v>
+        <v>0.9433455976724101</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01336444620897108</v>
+        <v>0.01335571115688277</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.4914513314276121</v>
+        <v>0.4923393625643067</v>
       </c>
       <c r="X38" t="n">
-        <v>0.0009347239555658149</v>
+        <v>0.0009339074883222234</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.7348320200682057</v>
+        <v>0.7351384632276249</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02483656657820433</v>
+        <v>0.02482221115691726</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.48142295121287</v>
+        <v>-0.4802497584636272</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01766589349197731</v>
+        <v>0.01765889697451369</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9951073955990873</v>
+        <v>0.9953271921121237</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.001623656702716062</v>
+        <v>0.001586766861866279</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-0.8713730627303744</v>
+        <v>-0.8562212999193628</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004518925452031933</v>
+        <v>0.004500594301272279</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.999999890415427</v>
+        <v>0.9999998041380312</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.32675995978336e-07</v>
+        <v>1.773751209348075e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1491847814540822</v>
+        <v>0.1521632323991432</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1339070738248205</v>
+        <v>0.1365513573779804</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.276604215929122</v>
       </c>
       <c r="P39" t="n">
-        <v>4.18810676199833</v>
+        <v>4.264388068889255</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9816306317010314</v>
+        <v>0.9816268711025765</v>
       </c>
       <c r="R39" t="n">
-        <v>0.009071978170132522</v>
+        <v>0.009072906735574798</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8558614183107447</v>
+        <v>0.8558176425002724</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01270694894657853</v>
+        <v>0.01270887839098529</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1404182545342846</v>
+        <v>0.1427950472409598</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001379355460289615</v>
+        <v>0.001377447141840691</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.04658790378515354</v>
+        <v>-0.04672596509918936</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01465324487178512</v>
+        <v>0.01465421133600714</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7565710180619907</v>
+        <v>0.7564767927545104</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005353982305837555</v>
+        <v>0.005355018402313135</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1162109480693672</v>
+        <v>-0.1164566034893098</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002179920818814901</v>
+        <v>0.002180160683826378</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4658,10 +4658,10 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2520765330787993</v>
+        <v>0.249459596754826</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4144678434159147</v>
+        <v>0.4060580165575136</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.314959883928858</v>
       </c>
       <c r="P40" t="n">
-        <v>4.621757819917251</v>
+        <v>4.519929776461174</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9938806243990306</v>
+        <v>0.9938311116255427</v>
       </c>
       <c r="R40" t="n">
-        <v>0.004698872054469673</v>
+        <v>0.004717843391356832</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9802671961778913</v>
+        <v>0.9797354819774584</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.00847727167766889</v>
+        <v>0.008590725492072768</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9615668136048001</v>
+        <v>0.9638233453426077</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0004460007926540083</v>
+        <v>0.0004327097056782412</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9825624626504067</v>
+        <v>0.9826533438533495</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.00331685034833121</v>
+        <v>0.00330819565323594</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.991921310995184</v>
+        <v>0.992448641969473</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.004036427315391123</v>
+        <v>0.003902466848552621</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999993533768033</v>
+        <v>0.9999997809895194</v>
       </c>
       <c r="AM40" t="n">
-        <v>4.889307680241457e-07</v>
+        <v>2.84547108624948e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4762,10 +4762,10 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2672649319402196</v>
+        <v>0.2573692229621695</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2880228810809274</v>
+        <v>0.2816395327127157</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.427001742671981</v>
       </c>
       <c r="P41" t="n">
-        <v>4.614031254374476</v>
+        <v>4.51040769462028</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9936351579933533</v>
+        <v>0.9936862574154206</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006183136298827306</v>
+        <v>0.006158265972016336</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8717627216438104</v>
+        <v>0.8714355505963176</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01042832045153212</v>
+        <v>0.0104416148351391</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.6000363904095842</v>
+        <v>0.5896632588938575</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001577184887911354</v>
+        <v>0.001597506265128528</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9683155944752773</v>
+        <v>0.9693153147744089</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.004772694571389385</v>
+        <v>0.004696795997337061</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9460267791472413</v>
+        <v>0.9471342693856056</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007489965703155551</v>
+        <v>0.007412723154435572</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.9022206683250865</v>
+        <v>0.9028596321955266</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001019947612705738</v>
+        <v>0.001016609597162556</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3046766718391037</v>
+        <v>0.3161275944552756</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4135605101589914</v>
+        <v>0.4155201972372792</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.505860970347477</v>
       </c>
       <c r="P42" t="n">
-        <v>4.604108097240657</v>
+        <v>4.560499203060885</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9664704829828186</v>
+        <v>0.9665756487176985</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01212587234476372</v>
+        <v>0.01210684093748995</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8845119886185325</v>
+        <v>0.8849506236851598</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.01864921974446343</v>
+        <v>0.01861377024741266</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.975262297923929</v>
+        <v>0.9636443743332248</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0008406400487310284</v>
+        <v>0.00101909861271533</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6752337043589152</v>
+        <v>0.6756110582638586</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01663230932561527</v>
+        <v>0.01662264377356529</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9874254179458843</v>
+        <v>0.9881447871972849</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.003467793859899984</v>
+        <v>0.003367139974697419</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.211558780060491</v>
+        <v>0.2145613387877751</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3837066024485357</v>
+        <v>0.3889771463935804</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.103051778684014</v>
+        <v>3.957269318509153</v>
       </c>
       <c r="P43" t="n">
-        <v>4.242933633256284</v>
+        <v>4.261918923283186</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.961363204168638</v>
+        <v>0.9613909978500171</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01201024004474685</v>
+        <v>0.01200591943751869</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9360594980811746</v>
+        <v>0.9359512872315633</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02174663885154189</v>
+        <v>0.02176503272872378</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.8444994357436967</v>
+        <v>0.8520911198452248</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.001862298631364919</v>
+        <v>0.001816270227262488</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7582988545113463</v>
+        <v>0.759371440608578</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01558005740793213</v>
+        <v>0.01554544951738278</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.9415780619938836</v>
+        <v>0.9435768883116423</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001354946447884544</v>
+        <v>0.001331565908907165</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9828529423963531</v>
+        <v>0.9834767256382397</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.000520387758631626</v>
+        <v>0.0005108346237562572</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5072,10 +5072,10 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1778728783246155</v>
+        <v>0.1729821644702371</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4109333048982851</v>
+        <v>0.3955313657661261</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.220618689085988</v>
       </c>
       <c r="P44" t="n">
-        <v>4.558173054027384</v>
+        <v>4.392844010909901</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9524928908463195</v>
+        <v>0.9519845256476372</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007423879822155539</v>
+        <v>0.007463494940070896</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9600113986324511</v>
+        <v>0.9586228785039925</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.008967353652920248</v>
+        <v>0.009121711403111717</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.9475647386169641</v>
+        <v>0.9455523891613016</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.002539587827044078</v>
+        <v>0.002587860918124825</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9046726860662117</v>
+        <v>0.9038505559368722</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01079871216890461</v>
+        <v>0.01084517779808726</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8499862486285047</v>
+        <v>0.8524112247880553</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.008414155947478238</v>
+        <v>0.008345871343629836</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.7109350540623469</v>
+        <v>0.7002634934257979</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001138778023100324</v>
+        <v>0.001159607947780862</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5176,10 +5176,10 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.399617491041528</v>
+        <v>0.402064738426252</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3335125677990796</v>
+        <v>0.3475688637037856</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.273822963139304</v>
       </c>
       <c r="P45" t="n">
-        <v>4.325380437067722</v>
+        <v>4.371840953772796</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9658853692187089</v>
+        <v>0.9658466124528553</v>
       </c>
       <c r="R45" t="n">
-        <v>0.00902049630345399</v>
+        <v>0.009025618827383747</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9718586955211752</v>
+        <v>0.9717844804701022</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01434830253796377</v>
+        <v>0.01436720995678839</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9213327097957723</v>
+        <v>0.9214806880545869</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007355931053651656</v>
+        <v>0.007349009306114705</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8706788013804121</v>
+        <v>0.8704565050127979</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008545790531278933</v>
+        <v>0.008553132260802921</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9206967997484848</v>
+        <v>0.9208076557519436</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008569930229382532</v>
+        <v>0.008563938286751661</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9798230439313416</v>
+        <v>0.9799171581444163</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006237150592537547</v>
+        <v>0.0006222587180918955</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5280,10 +5280,10 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4729359869420497</v>
+        <v>0.4152342674066459</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3951158336724084</v>
+        <v>0.3807848635863</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.736658907187545</v>
       </c>
       <c r="P46" t="n">
-        <v>4.587592058594874</v>
+        <v>4.48946306585675</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9589381830888655</v>
+        <v>0.9615264294618416</v>
       </c>
       <c r="R46" t="n">
-        <v>0.009661516124798633</v>
+        <v>0.009352063529390156</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9747217431325395</v>
+        <v>0.9776538414275411</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01225990247327328</v>
+        <v>0.01152696281645199</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9016747884732356</v>
+        <v>0.9041293457485774</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01163898316590088</v>
+        <v>0.01149278919874865</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9764606694056327</v>
+        <v>0.9787268952371752</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002511456156627498</v>
+        <v>0.002387503331102444</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8416483821832315</v>
+        <v>0.8489309668734064</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01317765173047614</v>
+        <v>0.01287106542646347</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9866561459926659</v>
+        <v>0.9867838400593032</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009977044662828614</v>
+        <v>0.0009929192221314999</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5384,10 +5384,10 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.251984504906933</v>
+        <v>0.249759804799666</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4093876944901919</v>
+        <v>0.4061826014847641</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.226749871470481</v>
       </c>
       <c r="P47" t="n">
-        <v>4.392775067952552</v>
+        <v>4.357803244108987</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9590464560947336</v>
+        <v>0.9589125222689501</v>
       </c>
       <c r="R47" t="n">
-        <v>0.007605115654284786</v>
+        <v>0.007617541328697981</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9579071079636191</v>
+        <v>0.9576731773183128</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01130436365149408</v>
+        <v>0.01133573204915898</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.9064354049713377</v>
+        <v>0.9063341516565808</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.004779371565915418</v>
+        <v>0.004781956926118184</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8523712870585474</v>
+        <v>0.8520133906469718</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01145620700581038</v>
+        <v>0.01147008524573142</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9708915793059046</v>
+        <v>0.9713339561655905</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.002645885754715205</v>
+        <v>0.002625703281329063</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9143863556007816</v>
+        <v>0.9146403158551536</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005590170462090796</v>
+        <v>0.0005581873096024894</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5488,10 +5488,10 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1259930651411941</v>
+        <v>0.112812893274769</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4676922627022872</v>
+        <v>0.4712448926497022</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.689594567822128</v>
       </c>
       <c r="P48" t="n">
-        <v>4.335721358768839</v>
+        <v>4.332382146406159</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9941999649462646</v>
+        <v>0.9942150638287417</v>
       </c>
       <c r="R48" t="n">
-        <v>0.003926842776993572</v>
+        <v>0.003921728189367217</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9965122258024854</v>
+        <v>0.9963374720407574</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.004318365597321497</v>
+        <v>0.004425228507921046</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.9446549304664328</v>
+        <v>0.9455904102927983</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.003974027023178182</v>
+        <v>0.003940298040925931</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9884163133860879</v>
+        <v>0.9886933385846548</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.006241422515784429</v>
+        <v>0.006166338720971824</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.9458595760652015</v>
+        <v>0.9449305151071618</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.001922816662753592</v>
+        <v>0.001939244453785518</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9998879115387178</v>
+        <v>0.9998872132943413</v>
       </c>
       <c r="AM48" t="n">
-        <v>8.197453231903187e-05</v>
+        <v>8.222946218451477e-05</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5592,10 +5592,10 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3817557588248525</v>
+        <v>0.3620994881251263</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4667823071664064</v>
+        <v>0.4637656770311649</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.033112792883243</v>
       </c>
       <c r="P49" t="n">
-        <v>4.419788125429537</v>
+        <v>4.394942862891178</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.932071578935464</v>
+        <v>0.9330972743352871</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0123538134184521</v>
+        <v>0.01226018952121035</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9452332951606957</v>
+        <v>0.9450246457949445</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01578560105759507</v>
+        <v>0.01581564234444936</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9509154053779656</v>
+        <v>0.9489030406969238</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002124625930669728</v>
+        <v>0.002167741049540636</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4329733516312154</v>
+        <v>0.4369628064539961</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01390198537167395</v>
+        <v>0.01385299363521287</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3487553446976571</v>
+        <v>0.3721399672767072</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01773095824693437</v>
+        <v>0.01740971013083599</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8701975943631495</v>
+        <v>0.8708018801775679</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.00131613683408995</v>
+        <v>0.001313069669741915</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5696,10 +5696,10 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5222632463286973</v>
+        <v>0.5100697585861687</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5592516851166626</v>
+        <v>0.5534890747704226</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.291959939524077</v>
       </c>
       <c r="P50" t="n">
-        <v>4.624536811391951</v>
+        <v>4.517901989223707</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9599360567777981</v>
+        <v>0.9646581004431101</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01069814289514025</v>
+        <v>0.01004792749893568</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9772907213610478</v>
+        <v>0.9852643325071451</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01267783235367612</v>
+        <v>0.01021240998622435</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9373826718554937</v>
+        <v>0.9385400938770382</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005331967793338138</v>
+        <v>0.005282459760951425</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.9489709504266232</v>
+        <v>0.949613260751951</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002307922123439729</v>
+        <v>0.002293351044626732</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8187472941085392</v>
+        <v>0.8189356378143295</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01708595308156951</v>
+        <v>0.01707707357789213</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5242408860059533</v>
+        <v>0.4766078924922043</v>
       </c>
       <c r="L51" t="n">
-        <v>0.551887474345802</v>
+        <v>0.5516876227432732</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.851203782657342</v>
       </c>
       <c r="P51" t="n">
-        <v>4.426261199085875</v>
+        <v>4.424936364643755</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9282916103455481</v>
+        <v>0.9284394557088755</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01075470950935025</v>
+        <v>0.01074361698339259</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9300399470027998</v>
+        <v>0.9297049037140779</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01563736320020485</v>
+        <v>0.01567476265628154</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7949488882956304</v>
+        <v>0.7956633511931013</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01445882061939311</v>
+        <v>0.01443360908798849</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8403089800580006</v>
+        <v>-0.8076971065108969</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003403153679433606</v>
+        <v>0.003372865476808775</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8905477554819972</v>
+        <v>0.8919091967836299</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01062199979512314</v>
+        <v>0.01055573125576267</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9952464338697469</v>
+        <v>0.9956305534453201</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005709001490599392</v>
+        <v>0.0005473480839950982</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5902,10 +5902,10 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1593376026831239</v>
+        <v>0.1562936953832578</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2471242617516075</v>
+        <v>0.2432115949197743</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.255272484088167</v>
       </c>
       <c r="P52" t="n">
-        <v>4.402205271170493</v>
+        <v>4.298583021057969</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9522689513239644</v>
+        <v>0.9525945332370921</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01055003142653106</v>
+        <v>0.0105139880429486</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.965573689926939</v>
+        <v>0.9660857974002085</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.008496514298236463</v>
+        <v>0.008433082707538257</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.7739383346892933</v>
+        <v>0.773926547449727</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.003363462404153451</v>
+        <v>0.003363550091334485</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7675048710061128</v>
+        <v>0.7692294411896498</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01731439699450017</v>
+        <v>0.01725006129873364</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3659677236386482</v>
+        <v>0.367799419229467</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01312748883495265</v>
+        <v>0.01310851270697796</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.03940591243185443</v>
+        <v>0.04072390418856464</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009449203906741122</v>
+        <v>0.0009442719249044745</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.331297244801841</v>
+        <v>0.3358214977156688</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2331365840842921</v>
+        <v>0.2369894245726382</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.452334897594409</v>
       </c>
       <c r="P53" t="n">
-        <v>4.350070108392953</v>
+        <v>4.414200628330695</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9798811561201866</v>
+        <v>0.9798716509251806</v>
       </c>
       <c r="R53" t="n">
-        <v>0.006098380259121431</v>
+        <v>0.006099820686040818</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9651652516941924</v>
+        <v>0.965172350531748</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.0108168468631426</v>
+        <v>0.01081574464545895</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.8125295352707419</v>
+        <v>0.810031119866949</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.004444737559709805</v>
+        <v>0.00447425700144224</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9846087356440815</v>
+        <v>0.9845986835733542</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003062915795661569</v>
+        <v>0.003063915831139631</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9640290593443713</v>
+        <v>0.9642202717139952</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005523177304828529</v>
+        <v>0.005508477841410778</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9535028366339573</v>
+        <v>0.9531433687948713</v>
       </c>
       <c r="AM53" t="n">
-        <v>9.54968113981249e-05</v>
+        <v>9.586524183558239e-05</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6110,10 +6110,10 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2292086573981105</v>
+        <v>0.2232363824600347</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4550656729641968</v>
+        <v>0.4375264112632372</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.144200181763916</v>
       </c>
       <c r="P54" t="n">
-        <v>4.472796999004565</v>
+        <v>4.316533435116456</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9380565442139962</v>
+        <v>0.9366030132557153</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009037514961835866</v>
+        <v>0.009142934786936875</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.9288596838849406</v>
+        <v>0.9261015759168229</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01374196267892449</v>
+        <v>0.014005817333021</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.7864333465299957</v>
+        <v>0.7887358602280492</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.002665070029321572</v>
+        <v>0.00265066471531907</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8060421491688397</v>
+        <v>0.8036608566898976</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01306081536098914</v>
+        <v>0.01314074700920427</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.7519430442451381</v>
+        <v>0.7507807586900389</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.006381944824503807</v>
+        <v>0.0063968788415862</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8703772792930199</v>
+        <v>0.8642805433697253</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001060721103793729</v>
+        <v>0.001085379711469188</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6214,10 +6214,10 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1960898588687952</v>
+        <v>0.196852432134677</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4637353297257206</v>
+        <v>0.4676882240271638</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.361472218356489</v>
       </c>
       <c r="P55" t="n">
-        <v>4.374590793080077</v>
+        <v>4.402559510476355</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.884735847416612</v>
+        <v>0.8850052417179333</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01369065973784698</v>
+        <v>0.01367465153775916</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.8312328792049783</v>
+        <v>0.8321391607880551</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.01983031059578343</v>
+        <v>0.01977699441235166</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.5529111450801742</v>
+        <v>0.5594442934092601</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.002927647246451476</v>
+        <v>0.002906178200845838</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.5157254216077696</v>
+        <v>0.5156977542095719</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.0222911780323355</v>
+        <v>0.02229181478895856</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.81293579498316</v>
+        <v>0.8128425269219781</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.00617746071905316</v>
+        <v>0.00617900053257729</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8432702132056595</v>
+        <v>0.8436896170382504</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0005484929880177256</v>
+        <v>0.000547758621669043</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6318,10 +6318,10 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2182594007781727</v>
+        <v>0.2062853367551514</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3909143464263679</v>
+        <v>0.3886907981446448</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.242619804626787</v>
+        <v>4.024244761351999</v>
       </c>
       <c r="P56" t="n">
-        <v>4.368716243102774</v>
+        <v>4.335874724164384</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8535469944905176</v>
+        <v>0.8545500202619801</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01122855025075698</v>
+        <v>0.01119003320147255</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.7525778361328166</v>
+        <v>0.7533589873120485</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.01736668347741985</v>
+        <v>0.01733924711215762</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>0.3086601203123401</v>
+        <v>0.3262060422775743</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.007287401834010887</v>
+        <v>0.007194331888172362</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6477174211148597</v>
+        <v>0.6484351885282893</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01569224771937461</v>
+        <v>0.01567625327655565</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8732122279873493</v>
+        <v>0.8803928136720532</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005176911909704549</v>
+        <v>0.005028178966376814</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8822178864965484</v>
+        <v>0.8821250911036076</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001626876690650353</v>
+        <v>0.00162751743708451</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6422,10 +6422,10 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3849234920957109</v>
+        <v>0.3797827501136171</v>
       </c>
       <c r="L57" t="n">
-        <v>0.461126682641225</v>
+        <v>0.4582444120870413</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.247766393668665</v>
       </c>
       <c r="P57" t="n">
-        <v>4.399277994960332</v>
+        <v>4.37449370847799</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9116510569896288</v>
+        <v>0.9121614084768805</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009038466687013042</v>
+        <v>0.009012323331070929</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.812367363536174</v>
+        <v>0.8132962131565457</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01639526086648921</v>
+        <v>0.01635462927421844</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.711278946138194</v>
+        <v>0.7126983537525658</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.007746387230646902</v>
+        <v>0.007727322413732051</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7476960203596653</v>
+        <v>0.7475439468977283</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007711170955396784</v>
+        <v>0.007713494517266502</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9449733708556105</v>
+        <v>0.9472210032347024</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004316828164042718</v>
+        <v>0.004227745852606556</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6875316757312995</v>
+        <v>0.6892384405335991</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001249457223210623</v>
+        <v>0.001246040157381087</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6526,10 +6526,10 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2134558972425616</v>
+        <v>0.2024072301870911</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5252564978602345</v>
+        <v>0.5061444885241897</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.10470435677508</v>
       </c>
       <c r="P58" t="n">
-        <v>4.739850973476084</v>
+        <v>4.417317337476732</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9721357093472135</v>
+        <v>0.969779090938868</v>
       </c>
       <c r="R58" t="n">
-        <v>0.007019307197002845</v>
+        <v>0.007310111744225025</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.990574249611337</v>
+        <v>0.9894655837610564</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.005633212420600209</v>
+        <v>0.005955296625892809</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.980109698181364</v>
+        <v>0.9867414870619635</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001298006048675786</v>
+        <v>0.001059750031214271</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.976660886302444</v>
+        <v>0.9758403265398836</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.005869974281978737</v>
+        <v>0.005972271584169496</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.7296900926998517</v>
+        <v>0.7047337141015073</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01333826099171613</v>
+        <v>0.01394039757509405</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9545845319029959</v>
+        <v>0.9523788416415666</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0007547591650641712</v>
+        <v>0.0007728700456659487</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6630,10 +6630,10 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4698313368793378</v>
+        <v>0.4652114978160279</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5173025978112151</v>
+        <v>0.5157910151339415</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.189896485281355</v>
       </c>
       <c r="P59" t="n">
-        <v>4.393915463190798</v>
+        <v>4.384984725234256</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.8024374949676303</v>
+        <v>0.8090252100858104</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01902519714862739</v>
+        <v>0.0187053106076517</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7672228798215391</v>
+        <v>0.7850738976500554</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03024558205162054</v>
+        <v>0.02906272834793005</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4795734377595594</v>
+        <v>0.4681752040379594</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02229404586562288</v>
+        <v>0.02253686245002089</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1462312943508465</v>
+        <v>0.1413049826947327</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.010719479843307</v>
+        <v>0.01075036147511836</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.7984893252777707</v>
+        <v>-0.7873784136543076</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01663495769319055</v>
+        <v>0.01658349341908137</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5650940897151631</v>
+        <v>-0.5568262532607748</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002518303487585613</v>
+        <v>0.002511643028074254</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6734,10 +6734,10 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3312705578089989</v>
+        <v>0.3216419994495925</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2854931841871585</v>
+        <v>0.2754641114172093</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.066724723170381</v>
       </c>
       <c r="P60" t="n">
-        <v>4.291643388097056</v>
+        <v>4.195073298832094</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8068778619076948</v>
+        <v>0.8116662969327862</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02733308009053523</v>
+        <v>0.02699209329262224</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.2699163625909837</v>
+        <v>0.2883718764323214</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.0598621383927522</v>
+        <v>0.05910067901708698</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.664051570494048</v>
+        <v>-1.657799549627808</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008650571714626725</v>
+        <v>0.008640415131379848</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6104184213497649</v>
+        <v>0.6223239458253429</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006883538457404796</v>
+        <v>0.00677754268735502</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-4.979845877138116</v>
+        <v>-4.89634677206556</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.005441023420024856</v>
+        <v>0.005402902226488513</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9494956580302899</v>
+        <v>0.9490885277054169</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004364569661711197</v>
+        <v>0.0004382126388825029</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6838,10 +6838,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3487925786240411</v>
+        <v>0.354482847122061</v>
       </c>
       <c r="L61" t="n">
-        <v>0.31595854253359</v>
+        <v>0.3236217673834675</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.865370088861562</v>
       </c>
       <c r="P61" t="n">
-        <v>4.176536665510469</v>
+        <v>4.231305426933169</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9463680041603295</v>
+        <v>0.9447594290620249</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01651113503026745</v>
+        <v>0.01675691354403788</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.896481492307235</v>
+        <v>0.8932288557403374</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.03585794501956721</v>
+        <v>0.03641693107707326</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.02150214429286945</v>
+        <v>0.01951775498147301</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.00536221190202193</v>
+        <v>0.005367646419100328</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6584248501871683</v>
+        <v>0.6555672291491994</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005921599870196677</v>
+        <v>0.005946318360254478</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.8583797538849819</v>
+        <v>0.8559920197379396</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.003008144526545886</v>
+        <v>0.003033397366743239</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.254124228904502</v>
+        <v>0.2578341800362859</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002352680363657656</v>
+        <v>0.002346822008842813</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6944,10 +6944,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.08057577359565576</v>
+        <v>0.08024552226375803</v>
       </c>
       <c r="L62" t="n">
-        <v>0.138529775175808</v>
+        <v>0.1381339878187344</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.141186837809406</v>
       </c>
       <c r="P62" t="n">
-        <v>4.13593340620653</v>
+        <v>4.162196773361142</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9891831520261556</v>
+        <v>0.9891079826175364</v>
       </c>
       <c r="R62" t="n">
-        <v>0.006859115717376115</v>
+        <v>0.006882907445634039</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.984580446180941</v>
+        <v>0.9844337879164503</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01295201186124832</v>
+        <v>0.01301346059979336</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.1384624764020728</v>
+        <v>-0.1401515107108542</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003552033840847688</v>
+        <v>0.003554667780729094</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.750249938717665</v>
+        <v>0.7502087479029408</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.006691074588615731</v>
+        <v>0.006691626339132252</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9686679513509983</v>
+        <v>0.9686188992059851</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002627847290375744</v>
+        <v>0.002629903509816402</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8411339879515929</v>
+        <v>0.8410207675549884</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.00199678677172279</v>
+        <v>0.001997498178529089</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7050,10 +7050,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2534807936850445</v>
+        <v>0.2554525714322202</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2836549067509452</v>
+        <v>0.2862074082137656</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.076109010387499</v>
+        <v>3.980842593650126</v>
       </c>
       <c r="P63" t="n">
-        <v>4.199074961353341</v>
+        <v>4.217261579853127</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9829085504581041</v>
+        <v>0.9827688126286818</v>
       </c>
       <c r="R63" t="n">
-        <v>0.009561889695743252</v>
+        <v>0.009600898609111327</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9652863075384963</v>
+        <v>0.9649717576232076</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.02051588020041751</v>
+        <v>0.02060862048660414</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.7209212981278978</v>
+        <v>0.7203217739104339</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.002306789128626304</v>
+        <v>0.002309265551940402</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9671794410622262</v>
+        <v>0.9672409336188823</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.002014825477001557</v>
+        <v>0.002012937104873775</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.7027205602551807</v>
+        <v>0.7036672958122212</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.004862549693123036</v>
+        <v>0.00485480072176</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.2447840862475307</v>
+        <v>0.2459152511012133</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002006908401343829</v>
+        <v>0.002005404861163218</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7156,10 +7156,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1904143601439689</v>
+        <v>0.1997197132401451</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2796232020721094</v>
+        <v>0.2892619500463863</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.711467818595111</v>
       </c>
       <c r="P64" t="n">
-        <v>4.148917296716289</v>
+        <v>4.226872715202777</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9772581243724823</v>
+        <v>0.9767762504767393</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01010401006763344</v>
+        <v>0.01021049506228999</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9643713538480191</v>
+        <v>0.9635346399040459</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01993462091331377</v>
+        <v>0.02016733788819036</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.3301117076731909</v>
+        <v>0.3035166962356732</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.004420104241572202</v>
+        <v>0.004506990812565222</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.443474214484032</v>
+        <v>0.4384643318008835</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.009077794461341522</v>
+        <v>0.009118562377234187</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9672863425067978</v>
+        <v>0.9673876908292794</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002610343332504407</v>
+        <v>0.002606296717787316</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8314456272144627</v>
+        <v>0.831947140194401</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002320673440616347</v>
+        <v>0.0023172184283091</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7262,10 +7262,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3009284206411491</v>
+        <v>0.3034647984070029</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3666209776017354</v>
+        <v>0.3724942244605007</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.907603328633307</v>
       </c>
       <c r="P65" t="n">
-        <v>4.211211411908002</v>
+        <v>4.260244269585109</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9718203692257925</v>
+        <v>0.9718564603301845</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01209150711195608</v>
+        <v>0.01208376152318062</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9513135412684783</v>
+        <v>0.9514031216366629</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02522548334504742</v>
+        <v>0.02520226591933868</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6574895709740871</v>
+        <v>0.6561951676162501</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003962963771908178</v>
+        <v>0.003970445056921395</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6592597290558355</v>
+        <v>0.6587521909123003</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008216121672708012</v>
+        <v>0.008222238418852921</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.8842910605071772</v>
+        <v>0.8832292466624121</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002934851316821716</v>
+        <v>0.002948286532865155</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5599602967209191</v>
+        <v>0.5606336110063638</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001895594151944371</v>
+        <v>0.001894143351912501</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7368,10 +7368,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2467331047886739</v>
+        <v>0.2512712524681031</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2941697425909144</v>
+        <v>0.303987838451985</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4.099154174190237</v>
+        <v>3.955403547984412</v>
       </c>
       <c r="P66" t="n">
-        <v>4.152280808125145</v>
+        <v>4.233530557733366</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9740867051249551</v>
+        <v>0.9734023404809052</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01088816922631202</v>
+        <v>0.01103100940212961</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9562487056607991</v>
+        <v>0.9549295411090574</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.02201791944590517</v>
+        <v>0.0223473903783781</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.5338362846643055</v>
+        <v>0.522246034208256</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.004208854182623718</v>
+        <v>0.004260855409984499</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6778378883795728</v>
+        <v>0.6751432117666203</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008671893586146152</v>
+        <v>0.008708085439359236</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9418487224223577</v>
+        <v>0.9419618121103369</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003353846474465051</v>
+        <v>0.003350583691165243</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8446629637263448</v>
+        <v>0.8450691520827578</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002181711112681528</v>
+        <v>0.002178856784605068</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4211240356731683</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3893359619496097</v>
+        <v>0.3997698344858632</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.407889787316897</v>
       </c>
       <c r="P67" t="n">
-        <v>4.256502300860816</v>
+        <v>4.345422306408049</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8504428616286153</v>
+        <v>0.8525283223387797</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02797147984266242</v>
+        <v>0.02777577468623323</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.7833047593440867</v>
+        <v>0.7848923290825796</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0008091640488250561</v>
+        <v>0.0008061945192351184</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.5824652112008134</v>
+        <v>0.5893867000004429</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06658180180607642</v>
+        <v>0.06602763115315909</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7410318234330544</v>
+        <v>0.7429593583918832</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.00278794918391176</v>
+        <v>0.002777554264768829</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6346938552458945</v>
+        <v>0.6313608152100949</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01325700823701654</v>
+        <v>0.01331734914401607</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8205353419040649</v>
+        <v>0.8054099352659447</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.008773307198940081</v>
+        <v>0.009135539502298827</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8555139374891017</v>
+        <v>0.8374267526895326</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001014444571821043</v>
+        <v>0.0001076068417155008</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7582,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4316687937084649</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3963632116393457</v>
+        <v>0.4166102059554699</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.511522348131344</v>
       </c>
       <c r="P68" t="n">
-        <v>4.182306170899118</v>
+        <v>4.352269501750476</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.743675409782757</v>
+        <v>0.7440927573902089</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03377358247694359</v>
+        <v>0.03374607620841535</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.5155986862884836</v>
+        <v>0.5167933888166578</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001138197449117216</v>
+        <v>0.001136792986735699</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.3004459105781626</v>
+        <v>0.3028493435110874</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.0813598050534587</v>
+        <v>0.08121992231825687</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.5020794264404653</v>
+        <v>0.5021183811289898</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003765868228882323</v>
+        <v>0.003765720915132895</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7048848602041738</v>
+        <v>0.691631281567803</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007988538797499892</v>
+        <v>0.008165950851645492</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.7157197427207227</v>
+        <v>0.6985801701883201</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.0120232946200894</v>
+        <v>0.01238043913676423</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.3691402357936542</v>
+        <v>0.3341717975594742</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007059039833030327</v>
+        <v>0.0007252042009551913</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7690,10 +7690,10 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1547738540766385</v>
+        <v>0.1562554941398337</v>
       </c>
       <c r="L69" t="n">
-        <v>0.1841770033720459</v>
+        <v>0.1861352270848367</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.301187016990273</v>
       </c>
       <c r="P69" t="n">
-        <v>4.259420405291464</v>
+        <v>4.304736348181783</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9673672266840373</v>
+        <v>0.9673355863360517</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01058750305531791</v>
+        <v>0.01059263457012876</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9389939095671191</v>
+        <v>0.9389258171915439</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01368356693671716</v>
+        <v>0.01369120131160974</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.3477957089613422</v>
+        <v>0.3483877229764311</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.005128580943798832</v>
+        <v>0.005126252776728942</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8469079603138678</v>
+        <v>0.8468597089458333</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01584420593094515</v>
+        <v>0.01584670261327996</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9162558649540055</v>
+        <v>0.9159461069000925</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.008780421886658767</v>
+        <v>0.008796645685422454</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5059646608172848</v>
+        <v>0.5061216104844813</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004335791511731253</v>
+        <v>0.004335102740062144</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7794,10 +7794,10 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.153202753067615</v>
+        <v>0.1527928836483235</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2672550325473306</v>
+        <v>0.2675271120949496</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.339893559122465</v>
       </c>
       <c r="P70" t="n">
-        <v>4.369178507900327</v>
+        <v>4.373194889845031</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9516049325832915</v>
+        <v>0.9515721611432411</v>
       </c>
       <c r="R70" t="n">
-        <v>0.01079576125398307</v>
+        <v>0.01079941589058032</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.8522265026427879</v>
+        <v>0.8520610381033237</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.0171647497538944</v>
+        <v>0.01717435689883341</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.8936172713931245</v>
+        <v>0.893309346381268</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003783432369289226</v>
+        <v>0.00378890398886918</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9402014807681064</v>
+        <v>0.940221987907637</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01110392785059646</v>
+        <v>0.0111020237121112</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8147223483628884</v>
+        <v>0.8146333345514486</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01205590445620204</v>
+        <v>0.01205880014581655</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7469314564335851</v>
+        <v>0.7471408191864253</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002270961181941129</v>
+        <v>0.002270021608309901</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7898,10 +7898,10 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3261006684563419</v>
+        <v>0.3251980729523765</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3397542059656078</v>
+        <v>0.3388538564529291</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.4265321563301</v>
       </c>
       <c r="P71" t="n">
-        <v>4.455720406385815</v>
+        <v>4.442648558535788</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9597574884279682</v>
+        <v>0.9597880614638961</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01095336943782979</v>
+        <v>0.0109492079010399</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9396208268734003</v>
+        <v>0.9398073718015236</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01462423801791988</v>
+        <v>0.01460162932946054</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7301765887058249</v>
+        <v>0.7299603223088129</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004601301161484185</v>
+        <v>0.004603144788583897</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9056649037036879</v>
+        <v>0.9057230426477835</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.00979582786542837</v>
+        <v>0.009792808804193242</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8405184804071526</v>
+        <v>0.8403717129968757</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01636789512480754</v>
+        <v>0.01637542490364737</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9361192691334477</v>
+        <v>0.9360775720841192</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009874035844921467</v>
+        <v>0.0009877257872836157</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -8002,10 +8002,10 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3263018165925168</v>
+        <v>0.3226988012903637</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4057073659283928</v>
+        <v>0.4017290501323692</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.500658295365612</v>
       </c>
       <c r="P72" t="n">
-        <v>4.557836250263496</v>
+        <v>4.513285792519836</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9521000864375787</v>
+        <v>0.9522085015583066</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01249819190960644</v>
+        <v>0.01248403989486677</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8353653065720884</v>
+        <v>0.8354727484216882</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01694640224662776</v>
+        <v>0.01694087166883833</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.7163337047512079</v>
+        <v>0.7156760303640204</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.005866602336025322</v>
+        <v>0.005873399196269812</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9507015972250976</v>
+        <v>0.9507472067077319</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006958031930854206</v>
+        <v>0.006954812499250478</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8458927568523126</v>
+        <v>0.8465011975139933</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.02022166532314077</v>
+        <v>0.02018170661824531</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.8991587038121629</v>
+        <v>0.8992003415007763</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001447921331181695</v>
+        <v>0.001447622374680859</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8106,10 +8106,10 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.07823057899988078</v>
+        <v>0.08013831924157826</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08458649562314287</v>
+        <v>0.08703404128132332</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.345718815687935</v>
       </c>
       <c r="P73" t="n">
-        <v>4.217326877099836</v>
+        <v>4.333874858928858</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9947748895243048</v>
+        <v>0.9947699944715903</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004807285045698981</v>
+        <v>0.004809536328713667</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9561852532822893</v>
+        <v>0.9561793796709384</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007186915130547454</v>
+        <v>0.00718739683744775</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6403534384966396</v>
+        <v>0.6414271255723738</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001198820005081077</v>
+        <v>0.001197029191837482</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9730780809852572</v>
+        <v>0.9730474336871866</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.005505119982943941</v>
+        <v>0.005508252543151468</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8223446275418672</v>
+        <v>0.8218614884701047</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005153517805578645</v>
+        <v>0.005160520620231417</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07506294351406551</v>
+        <v>-0.0748496756734609</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002365573346084606</v>
+        <v>0.002365338696687945</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8210,10 +8210,10 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08513405677699858</v>
+        <v>0.08375853066839459</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1547993498081189</v>
+        <v>0.1529671327592744</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.36397608937349</v>
       </c>
       <c r="P74" t="n">
-        <v>4.457102876030488</v>
+        <v>4.403509512828978</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9638328933224084</v>
+        <v>0.9638384190809758</v>
       </c>
       <c r="R74" t="n">
-        <v>0.009008910268404112</v>
+        <v>0.009008222033025953</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.734744500036399</v>
+        <v>0.7348329767247739</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.01230481592129123</v>
+        <v>0.01230276359784669</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8088772938042357</v>
+        <v>0.8090122836622878</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001452792485329479</v>
+        <v>0.001452279341454517</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8774262632217157</v>
+        <v>0.8774164594341005</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01378587580146203</v>
+        <v>0.01378642710674003</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8580562204517683</v>
+        <v>0.8581244659164741</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007617691398854195</v>
+        <v>0.007615859915312293</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.6982950277519067</v>
+        <v>0.6981017776391559</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002050274712564035</v>
+        <v>0.002050931235375082</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8314,10 +8314,10 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.210319821056764</v>
+        <v>0.2067664206129807</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2629764023632348</v>
+        <v>0.262466612229401</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.184661703848845</v>
       </c>
       <c r="P75" t="n">
-        <v>4.299646623551126</v>
+        <v>4.290524214380456</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9659944784755637</v>
+        <v>0.9659636846522492</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007282644251293839</v>
+        <v>0.007285940917589359</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8763673102557349</v>
+        <v>0.8759969434664582</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.0125643046399848</v>
+        <v>0.01258311002769126</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8890371948156326</v>
+        <v>0.8902524808209079</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002009969715260556</v>
+        <v>0.001998932624330572</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9204002222076457</v>
+        <v>0.9205078240962039</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007404712966898268</v>
+        <v>0.007399706479654176</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8681780132120976</v>
+        <v>0.8684768007298713</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006886989701911804</v>
+        <v>0.006879180253910074</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9729564459330939</v>
+        <v>0.9731388809329852</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.001011140858395798</v>
+        <v>0.001007724524160602</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8418,10 +8418,10 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.01998426772365844</v>
+        <v>0.02041481449548191</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02200773679061888</v>
+        <v>0.02255884293081964</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.335730785167194</v>
       </c>
       <c r="P76" t="n">
-        <v>4.219380572437561</v>
+        <v>4.319293977451697</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9927430208950898</v>
+        <v>0.9927416500394189</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005345498109928115</v>
+        <v>0.005346002972920062</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9145361248832635</v>
+        <v>0.9145185545879547</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.00831748611129118</v>
+        <v>0.008318341052496479</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.860769381153662</v>
+        <v>0.8607171015896948</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.001028757418643334</v>
+        <v>0.001028950544056184</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9604635875108082</v>
+        <v>0.960457066720408</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008393810776824514</v>
+        <v>0.008394502949186979</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9889600284019455</v>
+        <v>0.9889502385778371</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008830839367428488</v>
+        <v>0.000883475392491625</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5697578950234307</v>
+        <v>0.5697404228527605</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.00118192071723161</v>
+        <v>0.001181944715941405</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8522,10 +8522,10 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03972700182767472</v>
+        <v>0.0375161600995857</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0988966465371202</v>
+        <v>0.09109877828007409</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.235925950677315</v>
       </c>
       <c r="P77" t="n">
-        <v>4.561583967268006</v>
+        <v>4.251805020139015</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.976715697955995</v>
+        <v>0.9766838123591988</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009150391132144099</v>
+        <v>0.009156654275950997</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.8086723131747384</v>
+        <v>0.8064700717880768</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.007969282215014611</v>
+        <v>0.008015015453292237</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.08208382664366698</v>
+        <v>-0.1097340222524199</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.001017268653852094</v>
+        <v>0.001030183666321997</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.909925701638066</v>
+        <v>0.909900377340481</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01301036244294376</v>
+        <v>0.01301219123951124</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1740114038501255</v>
+        <v>0.1750922767891173</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01357226093176349</v>
+        <v>0.01356337782371721</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8776904656512881</v>
+        <v>0.8758796496595981</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007925888737633415</v>
+        <v>0.0007984345314874358</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8626,10 +8626,10 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02841134719532212</v>
+        <v>0.02699802811307632</v>
       </c>
       <c r="L78" t="n">
-        <v>0.08336691559023626</v>
+        <v>0.0790397260377876</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.377810298060794</v>
       </c>
       <c r="P78" t="n">
-        <v>4.646665560534422</v>
+        <v>4.386222610833368</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9789603541012899</v>
+        <v>0.9783904451258419</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01053297673822684</v>
+        <v>0.01067467895894601</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.3704905875951197</v>
+        <v>0.3697360126165589</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.00961832364870469</v>
+        <v>0.009624086527390198</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7264249293988285</v>
+        <v>0.6906053367269736</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006117939382519815</v>
+        <v>0.0006506138719584699</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8109154939646281</v>
+        <v>0.8028645969740215</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.0178822899688515</v>
+        <v>0.01825902039580381</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2267716650339258</v>
+        <v>-0.2376474446796117</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01166862865501843</v>
+        <v>0.01172023785490019</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.705756944870378</v>
+        <v>-1.725642576437441</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.002428654769048067</v>
+        <v>0.002437562982966849</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8730,10 +8730,10 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2899193890845111</v>
+        <v>0.2887378674060793</v>
       </c>
       <c r="L79" t="n">
-        <v>0.2910348174218514</v>
+        <v>0.2896789461350093</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.358789254115512</v>
       </c>
       <c r="P79" t="n">
-        <v>4.436479194916979</v>
+        <v>4.385411218924689</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9801398266256397</v>
+        <v>0.9805398779262914</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02073013356015597</v>
+        <v>0.02052028378665912</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9147615800787688</v>
+        <v>0.9163432795460734</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04534793220316707</v>
+        <v>0.04492521984156974</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3554011413736848</v>
+        <v>0.3459237322995101</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002259610661589636</v>
+        <v>0.002276161351722865</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9855235685133081</v>
+        <v>0.9871635279861676</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.00940306714509352</v>
+        <v>0.008854450549396849</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5687256323819083</v>
+        <v>0.5593185193344927</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.004963483548155998</v>
+        <v>0.005017324186440493</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9855765734086701</v>
+        <v>0.9862256853627619</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003853263271019935</v>
+        <v>0.003765559012547529</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8761048693083854</v>
+        <v>0.8740234792776144</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009405975251529201</v>
+        <v>0.009484654546243096</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1594873656769697</v>
+        <v>0.1595546616330362</v>
       </c>
       <c r="L80" t="n">
-        <v>0.18390882828683</v>
+        <v>0.1840450935700307</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.445589425954382</v>
       </c>
       <c r="P80" t="n">
-        <v>4.462066301610659</v>
+        <v>4.446009014318028</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9932096807226687</v>
+        <v>0.9932731795314036</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01138951828732425</v>
+        <v>0.0113361393854839</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9786897121861911</v>
+        <v>0.9788754491318208</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02318136706959092</v>
+        <v>0.02308012349968894</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7034867978320782</v>
+        <v>0.7019987906301915</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001456582109596674</v>
+        <v>0.001460232355615892</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9826490153734436</v>
+        <v>0.9831208631198295</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.008457119754840123</v>
+        <v>0.008341334461357996</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.724710910057258</v>
+        <v>0.7232724348419159</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.004365530755422401</v>
+        <v>0.004376921555140897</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9824809015415823</v>
+        <v>0.9827151395388187</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.007020539750174251</v>
+        <v>0.006973447969835452</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9730306628205246</v>
+        <v>0.9726013777166624</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.005380227623715929</v>
+        <v>0.005422878523955323</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8946,10 +8946,10 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2675416034712867</v>
+        <v>0.2672160292479843</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2424459491024605</v>
+        <v>0.2461893094758684</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.565126561556436</v>
       </c>
       <c r="P81" t="n">
-        <v>4.554994012640694</v>
+        <v>4.554905759427732</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9905799127056364</v>
+        <v>0.9907375823719937</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01318997091635467</v>
+        <v>0.01307912088022594</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9724382467840322</v>
+        <v>0.9730374839034356</v>
       </c>
       <c r="U81" t="n">
-        <v>0.0248794563296073</v>
+        <v>0.02460751024770663</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9734432261850787</v>
+        <v>0.9735865702716282</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.01074023366948368</v>
+        <v>0.01071120845530277</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.8184894907031021</v>
+        <v>0.8122120651235197</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.002587056570275316</v>
+        <v>0.002631412180757075</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9668857580711469</v>
+        <v>0.9671114570058318</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005838082766465016</v>
+        <v>0.005818153245732371</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9597292303725677</v>
+        <v>0.9599325355082032</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009734506934280834</v>
+        <v>0.009709903736804569</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1441638819194829</v>
+        <v>0.1476585777734352</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1690735488551482</v>
+        <v>0.1779486003915289</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.56381144856591</v>
       </c>
       <c r="P82" t="n">
-        <v>4.545359511707726</v>
+        <v>4.581373345847023</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9625890378122482</v>
+        <v>0.9634987131821567</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02609182769915548</v>
+        <v>0.02577265442699048</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.8954648127737709</v>
+        <v>0.8986288775067877</v>
       </c>
       <c r="U82" t="n">
-        <v>0.050478587699661</v>
+        <v>0.04970877636834458</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.8950519438605907</v>
+        <v>0.8959236790392618</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.02169151319485111</v>
+        <v>0.02160123669770234</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>-0.1783526330020295</v>
+        <v>-0.1560668513950476</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.003185971614020668</v>
+        <v>0.003155700205137652</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7613241300107862</v>
+        <v>0.7610768122425228</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01757616147291451</v>
+        <v>0.01758526539184303</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9762751156272076</v>
+        <v>0.9769425019968285</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.00813854626638013</v>
+        <v>0.00802326015226024</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1872142165502269</v>
+        <v>0.1893204027356125</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1608576544214377</v>
+        <v>0.1634266058404603</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.564646219566645</v>
       </c>
       <c r="P83" t="n">
-        <v>4.493974794999652</v>
+        <v>4.536174058062235</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9760721175207164</v>
+        <v>0.9761844962819626</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01851974107782693</v>
+        <v>0.01847620034728505</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9260363687485822</v>
+        <v>0.9265243363566215</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03524662187934822</v>
+        <v>0.03513016145849297</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9585649390322634</v>
+        <v>0.9586179704669509</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009815672843915312</v>
+        <v>0.009809389446916533</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2945157817924284</v>
+        <v>0.2944383579636647</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009387607564904062</v>
+        <v>0.009388122675349825</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9234748611500143</v>
+        <v>0.9234468865166462</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01061925295258059</v>
+        <v>0.01062119376946844</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8738425497004633</v>
+        <v>0.873688303543886</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01324147090019422</v>
+        <v>0.01324956325650039</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1659043674747134</v>
+        <v>0.168261400395764</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2357226305561208</v>
+        <v>0.2392951190050516</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.508063070964528</v>
       </c>
       <c r="P84" t="n">
-        <v>4.366165992009806</v>
+        <v>4.520851279602867</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9941311806411958</v>
+        <v>0.9947306388470482</v>
       </c>
       <c r="R84" t="n">
-        <v>0.008996345286545413</v>
+        <v>0.008524515940662752</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9914800630368471</v>
+        <v>0.9927419426496462</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01234529181044577</v>
+        <v>0.01139444999852478</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9942676666135103</v>
+        <v>0.9940969056185013</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.005165320857537253</v>
+        <v>0.005241691383021949</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.2582690528086682</v>
+        <v>0.2590606781900662</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.007797326051412945</v>
+        <v>0.007793164024025685</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9058734908361235</v>
+        <v>0.9172944531408367</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01264439584762582</v>
+        <v>0.01185248531875967</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9952721662889131</v>
+        <v>0.9953609395978528</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002214798686985028</v>
+        <v>0.002193906801246853</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2307899480131057</v>
+        <v>0.232384799749474</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2690020248060223</v>
+        <v>0.2782905441772863</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9368,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.4579287131415</v>
       </c>
       <c r="P85" t="n">
-        <v>4.441174563235467</v>
+        <v>4.497065890760551</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9788713178783314</v>
+        <v>0.9805986405922199</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0181661322926504</v>
+        <v>0.01740773827383034</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9403591259714565</v>
+        <v>0.9491154746544618</v>
       </c>
       <c r="U85" t="n">
-        <v>0.03135265174089611</v>
+        <v>0.02895977228546437</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.996936134044341</v>
+        <v>0.9943039542316575</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.004265584289878811</v>
+        <v>0.005816080150991643</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.2001604720270995</v>
+        <v>-0.1927799087396398</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01711934293077899</v>
+        <v>0.01706662279498498</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.6610462994340929</v>
+        <v>0.6634729868567384</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.0188039391306333</v>
+        <v>0.01873650625006663</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9973024334736607</v>
+        <v>0.9996007539848109</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.001482498782537625</v>
+        <v>0.0005703330755728907</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1218510305567165</v>
+        <v>0.1217276426814131</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1517110977613974</v>
+        <v>0.548252343981105</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9470,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.465527496290664</v>
       </c>
       <c r="P86" t="n">
-        <v>4.398937498013611</v>
+        <v>4.581111611572777</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9896438494333476</v>
+        <v>0.8814029662123379</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01213724514909964</v>
+        <v>0.04107313565112523</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9815923007659499</v>
+        <v>0.8100861392994358</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01885902761674619</v>
+        <v>0.06057562069434851</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9993806777410954</v>
+        <v>0.9962561741154657</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.001447591855191151</v>
+        <v>0.003559144394161952</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.4109087493901971</v>
+        <v>0.5784462124008252</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.0177797942165395</v>
+        <v>0.009718601274682612</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9858751908923007</v>
+        <v>-0.7682385120692303</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.006076239409444921</v>
+        <v>0.06798514155595548</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.975607673285286</v>
+        <v>0.9654345316830725</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.005075764619731553</v>
+        <v>0.006042213719740869</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1823831187847791</v>
+        <v>0.1836792919038959</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2856478658682653</v>
+        <v>0.2897898832411685</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9572,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.626284423183901</v>
       </c>
       <c r="P87" t="n">
-        <v>4.483850245672489</v>
+        <v>4.640097022354929</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9561592412838862</v>
+        <v>0.9575810697455271</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02347293985291315</v>
+        <v>0.02308916945910394</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9112442915703309</v>
+        <v>0.9137800842870558</v>
       </c>
       <c r="U87" t="n">
-        <v>0.03862943287355763</v>
+        <v>0.03807360341033582</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.9089430183851125</v>
+        <v>0.9044295049137443</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.01686538748874917</v>
+        <v>0.01727832412035614</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.6396145975663785</v>
+        <v>0.6318813551480504</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.007036722368692527</v>
+        <v>0.007111819540295957</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.2962826056882126</v>
+        <v>0.333906347676852</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.0296393003675749</v>
+        <v>0.02883609532154794</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9801606213884105</v>
+        <v>0.986049614531881</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.007086364331634237</v>
+        <v>0.005942272287041352</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2319557577696864</v>
+        <v>0.2310798297965026</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1725746472494996</v>
+        <v>0.1753763876980404</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9674,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.585737126599059</v>
       </c>
       <c r="P88" t="n">
-        <v>4.558860890758955</v>
+        <v>4.622357867172565</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9874586149354444</v>
+        <v>0.9875930915909575</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01312993017379896</v>
+        <v>0.01305934674979869</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9623555206985545</v>
+        <v>0.9628607252871669</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02445377801615478</v>
+        <v>0.02428913380964197</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9643600608530896</v>
+        <v>0.9665714674301151</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.01068149469275072</v>
+        <v>0.01034480261303945</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5296258922636472</v>
+        <v>0.5292271408097087</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004278143553368549</v>
+        <v>0.004279956530047157</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9649862651850751</v>
+        <v>0.9663906243619471</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.005577356959369242</v>
+        <v>0.005464361768466608</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9515651571492654</v>
+        <v>0.9481456890308845</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01002418678966485</v>
+        <v>0.01037200308022392</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9764,10 +9764,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3416216863722881</v>
+        <v>0.3391853656933783</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3075512869948218</v>
+        <v>0.3168741071271186</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9776,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.50704372858565</v>
       </c>
       <c r="P89" t="n">
-        <v>4.623343108250671</v>
+        <v>4.604623003407573</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9938746947313596</v>
+        <v>0.9950787838142697</v>
       </c>
       <c r="R89" t="n">
-        <v>0.009261787942379482</v>
+        <v>0.008301702887742093</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9880443895281315</v>
+        <v>0.9928338874139709</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01494267518190293</v>
+        <v>0.01156869286342268</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9906719744968167</v>
+        <v>0.9917894683747683</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.007360263637374713</v>
+        <v>0.006905325378730429</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7841418737365479</v>
+        <v>0.7712477100601002</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004502557221515881</v>
+        <v>0.004635085658713924</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9848853373122541</v>
+        <v>0.9828675022844365</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.002986970168083486</v>
+        <v>0.003180108932496803</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9409655913407391</v>
+        <v>0.9365111335651226</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01105674204847277</v>
+        <v>0.01146630145867534</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9866,10 +9866,10 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1998143343901099</v>
+        <v>0.226725035550164</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3854945386760895</v>
+        <v>0.4805611621302232</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9878,54 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.483427880631227</v>
       </c>
       <c r="P90" t="n">
-        <v>3.536281218756167</v>
+        <v>4.282245688652591</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9842719427804033</v>
+        <v>0.985456612282216</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01658354325456672</v>
+        <v>0.01594676443091195</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9664724403721409</v>
+        <v>0.968770809940952</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02965424413646303</v>
+        <v>0.02861977711843928</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9907388276605076</v>
+        <v>0.9922180759568158</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01243191535602585</v>
+        <v>0.01139589804942022</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8164211965029525</v>
+        <v>0.7980355159901387</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004881553941645299</v>
+        <v>0.005120169371456811</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9954889652884574</v>
+        <v>0.9878729345013798</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005115737113518759</v>
+        <v>0.000838779863944477</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9861582643282164</v>
+        <v>0.9876930109154459</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003856345276853486</v>
+        <v>0.003636273520163143</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>

--- a/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_True.xlsx
@@ -653,25 +653,25 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.231221769167109</v>
+        <v>0.1686476518132877</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2007211518461947</v>
+        <v>0.1782678696175507</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.423003083472088</v>
+        <v>4.417326970800064</v>
       </c>
       <c r="P2" t="n">
-        <v>4.425560250819469</v>
+        <v>4.423606444917017</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9918567268035426</v>
+        <v>0.9923185929359322</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0055470614871942</v>
+        <v>0.005387457630333382</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.98869250484893</v>
+        <v>0.9930656081563579</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007711435021981065</v>
+        <v>0.006038877052497628</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9996179105578975</v>
+        <v>0.999923681274521</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001286171589219084</v>
+        <v>5.748201025783209e-05</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9966850795360935</v>
+        <v>0.9973256494871625</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002429298774071136</v>
+        <v>0.002181993932010704</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9581644567964351</v>
+        <v>0.9496983233805315</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008703455009517067</v>
+        <v>0.009543555706483972</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7279095922182931</v>
+        <v>0.6534959090041803</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001569695941572063</v>
+        <v>0.001771385559958304</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -757,25 +757,25 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1221977047489524</v>
+        <v>0.07171408406676065</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1443142982267897</v>
+        <v>0.1017747453408085</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.306107642639816</v>
+        <v>4.300312826722086</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33746382545987</v>
+        <v>4.330254871049777</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9889990008559164</v>
+        <v>0.9893759016180103</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006378019382377876</v>
+        <v>0.00626780982827655</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9922047187864307</v>
+        <v>0.9946835779088421</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005673400404644776</v>
+        <v>0.004685298542443515</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.9997436944936144</v>
+        <v>0.999960875424946</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.920331231647279e-05</v>
+        <v>1.531682008072195e-05</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.972430530330863</v>
+        <v>0.9734730378349004</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.008053064352710118</v>
+        <v>0.007899338459095656</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8609634914468878</v>
+        <v>0.8512334992325841</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009043039693689204</v>
+        <v>0.009354112411553348</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3381051712068962</v>
+        <v>0.3103613710509273</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003319493436383504</v>
+        <v>0.003388348801641898</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -861,25 +861,25 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3697996722445903</v>
+        <v>0.362659486143853</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2434823022440334</v>
+        <v>0.2838742423074582</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.407250937879116</v>
+        <v>4.40660532000618</v>
       </c>
       <c r="P4" t="n">
-        <v>4.484256662032916</v>
+        <v>4.483748731152004</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.952126288759651</v>
+        <v>0.9516550856182854</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0143130641352328</v>
+        <v>0.01438333074252759</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9822948653116685</v>
+        <v>0.9840904510056468</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01171621190359204</v>
+        <v>0.01110622671645142</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9541461425661923</v>
+        <v>0.9839398722216592</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.002664992239114771</v>
+        <v>0.001577184530042624</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.271675611020961</v>
+        <v>0.2403298576299169</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02777600773069858</v>
+        <v>0.02836742572800265</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9854820987101983</v>
+        <v>0.9909048126148843</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004997867808762986</v>
+        <v>0.003955839576026527</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.3169282047793512</v>
+        <v>0.2182747767810168</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004188244401585439</v>
+        <v>0.004480494028373271</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -965,25 +965,25 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1827280879260966</v>
+        <v>0.1240122415911155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2173629647558321</v>
+        <v>0.1730197966317188</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.284288814452183</v>
+        <v>4.278006377028112</v>
       </c>
       <c r="P5" t="n">
-        <v>4.352672707714889</v>
+        <v>4.343997144183124</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9961863812255521</v>
+        <v>0.9958209748870051</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003655159881691033</v>
+        <v>0.003826266631587295</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9950768263004883</v>
+        <v>0.9949246180707729</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00502562653060317</v>
+        <v>0.005102723041777825</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999999303532935</v>
+        <v>0.9999998673379219</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.626317777467947e-06</v>
+        <v>2.244546025662165e-06</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.996570261593108</v>
+        <v>0.9966818341208157</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002722355128832427</v>
+        <v>0.002677708675504335</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9737911724939311</v>
+        <v>0.9688517885690783</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005382663587193134</v>
+        <v>0.005867998557034293</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9675076390776964</v>
+        <v>0.9687129536458051</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008404536600112487</v>
+        <v>0.0008247179024873692</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1069,25 +1069,25 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1686949453492942</v>
+        <v>0.1107046564138275</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2032196895738114</v>
+        <v>0.1513629262028119</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.342240366865149</v>
+        <v>4.335892868848197</v>
       </c>
       <c r="P6" t="n">
-        <v>4.389808818884189</v>
+        <v>4.383418280140046</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9748594133187256</v>
+        <v>0.9746355176978958</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009585131638762059</v>
+        <v>0.009627718394340701</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9806330858151963</v>
+        <v>0.9826917087310015</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008027373072053283</v>
+        <v>0.007588751479548651</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9997436850972771</v>
+        <v>0.9999623731861246</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.276009850895156e-05</v>
+        <v>1.638326630847039e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9878096976082793</v>
+        <v>0.9879329784330714</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004528462023650734</v>
+        <v>0.004505505617394693</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6773249744471392</v>
+        <v>0.6672225791988857</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01845430180980078</v>
+        <v>0.01874096147373081</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.416379044741942</v>
+        <v>0.3778495548131363</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001800184854132759</v>
+        <v>0.001858657523372629</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1173,25 +1173,25 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1697000243333415</v>
+        <v>0.1516173739293405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1648970046130869</v>
+        <v>0.1423890590546853</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.332467324133582</v>
+        <v>4.323072234530487</v>
       </c>
       <c r="P7" t="n">
-        <v>4.35956137579332</v>
+        <v>4.355146584702293</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9859943408612178</v>
+        <v>0.9859405080665284</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007190558966467463</v>
+        <v>0.007204364694503113</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9842741824144735</v>
+        <v>0.984699910093058</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00951454561139514</v>
+        <v>0.009384873584252079</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9859438385817348</v>
+        <v>0.9981214537413815</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0005114937388193356</v>
+        <v>0.0001869897930280336</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9193479855511263</v>
+        <v>0.9168688105617283</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01132147323832901</v>
+        <v>0.01149416248112718</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9963504404849115</v>
+        <v>0.9985214486633248</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001590829917537565</v>
+        <v>0.001012562241913247</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.2867654836834522</v>
+        <v>0.2474881834295092</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004458529686701029</v>
+        <v>0.004579648526112375</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1277,25 +1277,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1487814895648295</v>
+        <v>0.1163738173577296</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1643432844717302</v>
+        <v>0.13729217252898</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.46691264392827</v>
+        <v>4.459073131503994</v>
       </c>
       <c r="P8" t="n">
-        <v>4.408244358875646</v>
+        <v>4.410109540493368</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9919380527634488</v>
+        <v>0.9929032330268159</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004837131010806054</v>
+        <v>0.004538351683090427</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9898702488707458</v>
+        <v>0.9908089679750506</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.006715912376889003</v>
+        <v>0.006397168251923677</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9998830110199964</v>
+        <v>0.999997682057544</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.099529602858357e-05</v>
+        <v>9.993288427451218e-06</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9860347330505472</v>
+        <v>0.9875701913274101</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005851714786929574</v>
+        <v>0.005520656817455708</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9833584222668272</v>
+        <v>0.9862207742088995</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005462346216131495</v>
+        <v>0.004970434819358465</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9997548019790157</v>
+        <v>0.9991807071320056</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.720022198237029e-05</v>
+        <v>0.000104558374468241</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1381,25 +1381,25 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1638384053732252</v>
+        <v>0.1542818023745993</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1616259254391911</v>
+        <v>0.145215259472402</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.269965407827312</v>
+        <v>4.264031022832119</v>
       </c>
       <c r="P9" t="n">
-        <v>4.356424141651297</v>
+        <v>4.351087997124465</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9933836391401224</v>
+        <v>0.9927380685104683</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004399175200757764</v>
+        <v>0.004608798705507943</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9902465280863846</v>
+        <v>0.9909303431413061</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007128432464503286</v>
+        <v>0.006874005080298568</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9995420389415455</v>
+        <v>0.9999917345320261</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001225581135728245</v>
+        <v>1.646499170082305e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.999776735421138</v>
+        <v>0.9998173053473225</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006046136348618595</v>
+        <v>0.000546928986538354</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9729178945644251</v>
+        <v>0.9643081571960751</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006209303929374495</v>
+        <v>0.007128303653031367</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9843089361077836</v>
+        <v>0.9789535800230732</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007531414802217934</v>
+        <v>0.0008722470078787164</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1485,25 +1485,25 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2045760244746017</v>
+        <v>0.1626744216582501</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1179390585897766</v>
+        <v>0.1119405598365042</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.174498702949626</v>
+        <v>4.162069417286844</v>
       </c>
       <c r="P10" t="n">
-        <v>4.218389167765724</v>
+        <v>4.209422659757757</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9859838478021674</v>
+        <v>0.9862298688532499</v>
       </c>
       <c r="R10" t="n">
-        <v>0.007520465275615061</v>
+        <v>0.007454170912605822</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.987979616375028</v>
+        <v>0.9891901895048216</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.009697733621253734</v>
+        <v>0.009196448156952712</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999226822629682</v>
+        <v>0.9999971097985998</v>
       </c>
       <c r="AD10" t="n">
-        <v>7.349597362621352e-05</v>
+        <v>1.420980224099927e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9081271632801182</v>
+        <v>0.902467984338404</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01239374183341249</v>
+        <v>0.01276975255260423</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9660960378853024</v>
+        <v>0.98906231097167</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002913228586725021</v>
+        <v>0.001654672778429981</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7924590047267251</v>
+        <v>0.7623843252788804</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002791621015718941</v>
+        <v>0.002987046992040119</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1589,25 +1589,25 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.149201674972049</v>
+        <v>0.1501508153581676</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3042608521164594</v>
+        <v>0.3097412275013239</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.076850431013222</v>
+        <v>4.073295245127875</v>
       </c>
       <c r="P11" t="n">
-        <v>4.249525989654821</v>
+        <v>4.249925105853993</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9927342809764135</v>
+        <v>0.9940305100751653</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00634133726390207</v>
+        <v>0.005747912707859695</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9892903729241561</v>
+        <v>0.9912662449360934</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0129389106506787</v>
+        <v>0.01168452450393584</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9794387791119039</v>
+        <v>0.9918994533391498</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001009999479786321</v>
+        <v>0.0006339483338074523</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9595744122075853</v>
+        <v>0.9634337785501598</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003564076620590171</v>
+        <v>0.003389681578452057</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9500994871820255</v>
+        <v>0.9575482384112401</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002510184108685442</v>
+        <v>0.002315266187414517</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9688265348984452</v>
+        <v>0.970288286620815</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.000747973372044176</v>
+        <v>0.0007302262584744992</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1693,25 +1693,25 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09975764557508192</v>
+        <v>0.08303556085308046</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1656875470041076</v>
+        <v>0.1269985914404088</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.05812402486322</v>
+        <v>4.064957109306907</v>
       </c>
       <c r="P12" t="n">
-        <v>4.120997695165938</v>
+        <v>4.106333946008106</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.945533999647139</v>
+        <v>0.9381214988030472</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02539949317205216</v>
+        <v>0.02707273930810015</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.6935125424392137</v>
+        <v>0.6531590003899861</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0547244311336627</v>
+        <v>0.05821569908717121</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9871473859788719</v>
+        <v>0.9996124404416791</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0002662360177207508</v>
+        <v>4.623174670768962e-05</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9986764530665788</v>
+        <v>0.9893742605548724</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001375666684079948</v>
+        <v>0.003897832099455253</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.2648964248668589</v>
+        <v>0.1507571027621</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.003725024688202526</v>
+        <v>0.004003785952431616</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9883604535002856</v>
+        <v>0.984713455162938</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002182447832766946</v>
+        <v>0.0002501096843459986</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1797,25 +1797,25 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1219723482576723</v>
+        <v>0.1046052363559759</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2090384686883623</v>
+        <v>0.1781095263305929</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.289380695969488</v>
+        <v>4.284498936397276</v>
       </c>
       <c r="P13" t="n">
-        <v>4.509167032838435</v>
+        <v>4.512167463987365</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9975489251894432</v>
+        <v>0.9975420965597387</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002833159398296388</v>
+        <v>0.002837103208448424</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.7859972271476799</v>
+        <v>0.7852518649838933</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003647291392042863</v>
+        <v>0.003653637528465981</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9984871601511938</v>
+        <v>0.9968010738754048</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.978705150908228e-05</v>
+        <v>4.331448389526533e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.572831286104469</v>
+        <v>0.5733592734007166</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004673707951291557</v>
+        <v>0.004670818653905619</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9999881277817543</v>
+        <v>0.9999986159566189</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0001392033902400646</v>
+        <v>4.75290057152836e-05</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9517830277239331</v>
+        <v>0.9507288043081396</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002228769955838406</v>
+        <v>0.002253003293152186</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1901,25 +1901,25 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1913164990551056</v>
+        <v>0.1423061650191516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2977137660328253</v>
+        <v>0.2373952058368417</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.361494374090167</v>
+        <v>4.34857888340721</v>
       </c>
       <c r="P14" t="n">
-        <v>4.373232155389765</v>
+        <v>4.36513594198754</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9799160865309536</v>
+        <v>0.9784575486770511</v>
       </c>
       <c r="R14" t="n">
-        <v>0.008439550996821529</v>
+        <v>0.00874062989140933</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9520278104195266</v>
+        <v>0.9442447185420917</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01089000787048949</v>
+        <v>0.01174022524168404</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.8287003913264104</v>
+        <v>0.9384407690311025</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.00202976038465065</v>
+        <v>0.001216783128968773</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9933409845184025</v>
+        <v>0.9890681643427042</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.003526743825810193</v>
+        <v>0.004518720187138739</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.5734291701102299</v>
+        <v>0.5710453581647299</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01475875823316106</v>
+        <v>0.01479993911678283</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.1895255856938327</v>
+        <v>0.1732252973868124</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001777368814722072</v>
+        <v>0.001795153083845376</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2005,25 +2005,25 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.18717447583358</v>
+        <v>0.1304836268708661</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2802587248821268</v>
+        <v>0.225077417760841</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.078910665279218</v>
+        <v>4.071216775025594</v>
       </c>
       <c r="P15" t="n">
-        <v>4.254817618534121</v>
+        <v>4.236127858148102</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.978939470265888</v>
+        <v>0.9786567316037734</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007669345042821305</v>
+        <v>0.007720654078001659</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9523521479509817</v>
+        <v>0.9520273347145426</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01074847518041454</v>
+        <v>0.01078504892243355</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.05221748830324335</v>
+        <v>0.09642079705258144</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.002684186241680081</v>
+        <v>0.002487384944832175</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.920673876493834</v>
+        <v>0.9198472231132222</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01031315796855143</v>
+        <v>0.0103667551023056</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.6376043548420356</v>
+        <v>0.6151955026472616</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.006737371933681222</v>
+        <v>0.006942551512348457</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999999861731875</v>
+        <v>0.9999999794528703</v>
       </c>
       <c r="AM15" t="n">
-        <v>4.351313172522935e-07</v>
+        <v>5.304383139919756e-07</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2109,25 +2109,25 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5236690839066376</v>
+        <v>0.5116905935028913</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5447407781101302</v>
+        <v>0.5580106590770122</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.405739545165345</v>
+        <v>4.397292039063695</v>
       </c>
       <c r="P16" t="n">
-        <v>4.587988865286516</v>
+        <v>4.543905353949662</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9764932249988238</v>
+        <v>0.9774541672102014</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009325216342966111</v>
+        <v>0.009132623035920969</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9942086516286338</v>
+        <v>0.9948384004568787</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005609887114394181</v>
+        <v>0.00529610309687222</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9601817919991722</v>
+        <v>0.9634493515656325</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004112766733193757</v>
+        <v>0.003940404129888298</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9084533900052759</v>
+        <v>0.9041059784958665</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003632957109193859</v>
+        <v>0.00371821846625235</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8464648288755372</v>
+        <v>0.8519298887371651</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01775503116466925</v>
+        <v>0.01743617429239267</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2211,25 +2211,25 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1754337283424276</v>
+        <v>0.1561989488837014</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2580489919528897</v>
+        <v>0.2088924470740592</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.87520233994104</v>
+        <v>3.852813853820157</v>
       </c>
       <c r="P17" t="n">
-        <v>4.032109036058404</v>
+        <v>4.001591897868716</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9920879992474081</v>
+        <v>0.9917890870424584</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004128955510096162</v>
+        <v>0.004206227587427231</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9799998131293119</v>
+        <v>0.9783098477163757</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.007114581269888968</v>
+        <v>0.007409068639950985</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.7280412325566102</v>
+        <v>0.8003200254921059</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001612865244953714</v>
+        <v>0.001382018344358574</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9935022091777753</v>
+        <v>0.9928446308328835</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002180010499502885</v>
+        <v>0.002287661406954993</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>-0.009983428235382341</v>
+        <v>0.02409766449063688</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005171791056765838</v>
+        <v>0.005083783199624289</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9944111180408979</v>
+        <v>0.9938089955965528</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0007231172551854027</v>
+        <v>0.0007610738708346899</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2315,25 +2315,25 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2418615173003435</v>
+        <v>0.1810731846415948</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2681713861606304</v>
+        <v>0.2181396130054191</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.288454172770764</v>
+        <v>4.276187403986832</v>
       </c>
       <c r="P18" t="n">
-        <v>4.303901155160221</v>
+        <v>4.291831088118254</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.985026502892796</v>
+        <v>0.9851734388559844</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006328491548989255</v>
+        <v>0.0062973640332368</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9274006724570588</v>
+        <v>0.9279085314307742</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01383690077720659</v>
+        <v>0.01378841875660756</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9988944085935337</v>
+        <v>0.9977919041162236</v>
       </c>
       <c r="AD18" t="n">
-        <v>9.158102257762326e-05</v>
+        <v>0.0001294246875996837</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9975720017418588</v>
+        <v>0.9975309717883521</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001478957117696714</v>
+        <v>0.001491400965814024</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9769438024956949</v>
+        <v>0.9793255483884311</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002554486911816233</v>
+        <v>0.002418949723355836</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9952075988858086</v>
+        <v>0.9949941545294427</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.000260957252360046</v>
+        <v>0.00026670521787285</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2419,25 +2419,25 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1612348717429317</v>
+        <v>0.1079340709237017</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2283845797447064</v>
+        <v>0.1727435974744558</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.995533644292064</v>
+        <v>4.005920821418274</v>
       </c>
       <c r="P19" t="n">
-        <v>4.383591224703615</v>
+        <v>4.377035453154457</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9875825126842892</v>
+        <v>0.9875701465441891</v>
       </c>
       <c r="R19" t="n">
-        <v>0.007851289867939881</v>
+        <v>0.007855198307420121</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.710156516457392</v>
+        <v>0.7114765431285616</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.008016189335489678</v>
+        <v>0.007997914529088962</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>0.174744410865898</v>
+        <v>0.1837341545961559</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.002706458036445235</v>
+        <v>0.002691676563138029</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7274633092627021</v>
+        <v>0.7260256418370703</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01473472129088299</v>
+        <v>0.01477353400067519</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8536031969239449</v>
+        <v>0.85719378358859</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004414265229393905</v>
+        <v>0.004359796154209266</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9962789382458113</v>
+        <v>0.994874388597629</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001783461555048031</v>
+        <v>0.0002093163489959056</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2523,25 +2523,25 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2693988039088081</v>
+        <v>0.2045934972566862</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2995141343496358</v>
+        <v>0.2445442201264004</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.607232881973829</v>
+        <v>4.607241387038218</v>
       </c>
       <c r="P20" t="n">
-        <v>4.593845696015604</v>
+        <v>4.598783453531802</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9762962510084028</v>
+        <v>0.976612397315219</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009038955024765819</v>
+        <v>0.008978474620503527</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8968608003763588</v>
+        <v>0.8966534456259784</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.009355787278112298</v>
+        <v>0.009365187155475274</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8330609224095268</v>
+        <v>0.8433897932619063</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002787967622029889</v>
+        <v>0.002700341882851749</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9570038691571811</v>
+        <v>0.965511589808925</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.005533113222151439</v>
+        <v>0.004955545378856197</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7908000271674109</v>
+        <v>0.7901322687689684</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01679629362026933</v>
+        <v>0.01682307883728081</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4643581990916192</v>
+        <v>0.4488825682907097</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006922422527367349</v>
+        <v>0.000702171094890019</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2627,25 +2627,25 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.120044065289244</v>
+        <v>0.07219559147808233</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1354346365046291</v>
+        <v>0.1377719211491936</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.099687029519429</v>
+        <v>4.140908318302595</v>
       </c>
       <c r="P21" t="n">
-        <v>4.124831078561143</v>
+        <v>4.145842200642549</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8659344877616386</v>
+        <v>0.7624758785289435</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02382863897532373</v>
+        <v>0.03171717961349629</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9306633375099265</v>
+        <v>0.9311838994173115</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01034354125347507</v>
+        <v>0.01030463973978849</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9974187279747142</v>
+        <v>0.9955573609107656</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.001677078333553553</v>
+        <v>0.002200173743795349</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.879834502240177</v>
+        <v>-8.387750498422248</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04838506855308401</v>
+        <v>0.06711036245885788</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.3346792842067901</v>
+        <v>-0.4270672450151185</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01968730175858778</v>
+        <v>0.020357289667859</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.5197619066445416</v>
+        <v>0.3917437025314507</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0007169590379083107</v>
+        <v>0.000806880737041819</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2731,25 +2731,25 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2811593684201072</v>
+        <v>0.2535001507163447</v>
       </c>
       <c r="L22" t="n">
-        <v>0.321775101569801</v>
+        <v>0.2746508064730541</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.136621870834812</v>
+        <v>4.128946614370499</v>
       </c>
       <c r="P22" t="n">
-        <v>4.310076641693127</v>
+        <v>4.297676854868168</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9820647239956858</v>
+        <v>0.9817979637015438</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006769864339093113</v>
+        <v>0.006820024296797402</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8978847682687321</v>
+        <v>0.8976312250391565</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.00942094307133092</v>
+        <v>0.009432631503570857</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9298081422905806</v>
+        <v>0.8657191579816775</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001468463497998433</v>
+        <v>0.002031078996908034</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3418109742691106</v>
+        <v>0.3371269343499832</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01119777150352522</v>
+        <v>0.01123754567250611</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.956446695636878</v>
+        <v>0.9553328018568251</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002988251203598708</v>
+        <v>0.003026222820744499</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7804140096473513</v>
+        <v>0.7749118057285759</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001981168985584216</v>
+        <v>0.002005836675365275</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2835,25 +2835,25 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2096861360727826</v>
+        <v>0.1847131896747425</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2752406104882666</v>
+        <v>0.2348782723470941</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.857921490702031</v>
+        <v>3.850086826112817</v>
       </c>
       <c r="P23" t="n">
-        <v>4.107349822216892</v>
+        <v>4.085623194454493</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9810167656443608</v>
+        <v>0.9808675953638107</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01031510513267665</v>
+        <v>0.01035555388123375</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8929865752045899</v>
+        <v>0.8921404542629828</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02293360548523138</v>
+        <v>0.02302409134101606</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.6467037899344668</v>
+        <v>-0.4475501605873478</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001225441781162331</v>
+        <v>0.001148951646470919</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9851183846284315</v>
+        <v>0.9849260945595132</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002054687130006122</v>
+        <v>0.002067919145075479</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.8793314987716929</v>
+        <v>0.8197786939038649</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.000563981449851673</v>
+        <v>0.0006892407272887055</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9993002898881095</v>
+        <v>0.9996652084584782</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001232359591140869</v>
+        <v>8.524435216033151e-05</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2939,25 +2939,25 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3822690760043342</v>
+        <v>0.3277679418815057</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4469060831203862</v>
+        <v>0.4275140448805302</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.250849247723202</v>
+        <v>4.117347210101763</v>
       </c>
       <c r="P24" t="n">
-        <v>4.315438599653929</v>
+        <v>4.262053242593149</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9923262185718489</v>
+        <v>0.992093086802033</v>
       </c>
       <c r="R24" t="n">
-        <v>0.00520225163414097</v>
+        <v>0.005280683381997648</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9991068166061686</v>
+        <v>0.9988587684328842</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.002398241356930686</v>
+        <v>0.00271087477256198</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9382511292855351</v>
+        <v>0.9284532361863773</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003923407368471433</v>
+        <v>0.004223221801649163</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8421435473736182</v>
+        <v>0.844462898264602</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009791283021592425</v>
+        <v>0.009719086298745199</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.994284036697847</v>
+        <v>0.9738738418658781</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0005108020693029962</v>
+        <v>0.001092058003510861</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3041,25 +3041,25 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2154668003430986</v>
+        <v>0.1551151330948538</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2294009511087869</v>
+        <v>0.1744703812059805</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.303014593509248</v>
+        <v>4.304155391582155</v>
       </c>
       <c r="P25" t="n">
-        <v>4.342456320621022</v>
+        <v>4.342596472878667</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.984922041146198</v>
+        <v>0.9858015368040433</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02036456638518282</v>
+        <v>0.01976171175503121</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1434164159467208</v>
+        <v>-0.06199570052996695</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03936908168833141</v>
+        <v>0.03794149614588624</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5380471058984511</v>
+        <v>0.5430990778423286</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008624123670844852</v>
+        <v>0.0008576836809241291</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8975779533860648</v>
+        <v>0.8946973609903511</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01103279726805333</v>
+        <v>0.01118686869107801</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.654847948708293</v>
+        <v>0.4720844054493026</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002879075660041329</v>
+        <v>0.003560656625274943</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9699181221291553</v>
+        <v>0.8476114331325391</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002841130519595289</v>
+        <v>0.006394622474124349</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9748671958439692</v>
+        <v>0.8774707171353237</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0009901843108232609</v>
+        <v>0.002186328936985769</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02271122221175204</v>
+        <v>-0.01696626943183022</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003348788921675589</v>
+        <v>0.003339369946215831</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3153,25 +3153,25 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3206536186429215</v>
+        <v>0.2666797233848718</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3143837239406004</v>
+        <v>0.2628449238673618</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.234787854458681</v>
+        <v>4.221753200887219</v>
       </c>
       <c r="P26" t="n">
-        <v>4.297137267092482</v>
+        <v>4.284261907213864</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9805752566094734</v>
+        <v>0.9810544005470457</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02142224457626787</v>
+        <v>0.02115638705318062</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.2919906370964104</v>
+        <v>0.3105216157772431</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04132120211662515</v>
+        <v>0.04077685948658304</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3275677251190763</v>
+        <v>-0.2486632755031415</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008077152767758603</v>
+        <v>0.0007833441845711382</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9471432283199523</v>
+        <v>0.9461188434167138</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01241231791554477</v>
+        <v>0.01253201851669864</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.2504148276689557</v>
+        <v>-0.2007638000944703</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003834165315760165</v>
+        <v>0.003757271428454402</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9040329216646996</v>
+        <v>0.9054657001735484</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.004146622618851097</v>
+        <v>0.004115551874939793</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9975319164238524</v>
+        <v>0.9958832148577317</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.0004226100857984786</v>
+        <v>0.0005458069104573922</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4587902950732933</v>
+        <v>0.4385600723309638</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001019418494247144</v>
+        <v>0.001038296447229953</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3265,25 +3265,25 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2430405588533768</v>
+        <v>0.1844609830677478</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3051947099590636</v>
+        <v>0.2508455450813917</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.135167174011909</v>
+        <v>4.115975320209331</v>
       </c>
       <c r="P27" t="n">
-        <v>4.152397114719814</v>
+        <v>4.127799914308075</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9961713086661211</v>
+        <v>0.9961265758893897</v>
       </c>
       <c r="R27" t="n">
-        <v>0.01004276530760784</v>
+        <v>0.01010126260673971</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.8975561274551627</v>
+        <v>0.8957071969081456</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01680212952590892</v>
+        <v>0.01695307584000439</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.70391716480052</v>
+        <v>0.7407668032794581</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006097876211079581</v>
+        <v>0.0005705809872169323</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9093238988441408</v>
+        <v>0.9103199826439793</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01276897068174134</v>
+        <v>0.01269864294462092</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9416527866436839</v>
+        <v>0.9554214681304803</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0008833008858315042</v>
+        <v>0.0007720785503271705</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8852490554518301</v>
+        <v>0.8849666163654676</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009463010752537832</v>
+        <v>0.009474649387084522</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.6135405126304565</v>
+        <v>0.5971030241113661</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003349172526138858</v>
+        <v>0.003419656899049005</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4392080963373839</v>
+        <v>0.439436006622564</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004876027065570017</v>
+        <v>0.004875036145022214</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3377,25 +3377,25 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3989682187359773</v>
+        <v>0.3641271367988411</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4092044112436037</v>
+        <v>0.395706256416794</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.115059320054375</v>
+        <v>4.118047418263454</v>
       </c>
       <c r="P28" t="n">
-        <v>4.291920661630636</v>
+        <v>4.286708922050352</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9444724491243617</v>
+        <v>0.9431002139853811</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02453905954847143</v>
+        <v>0.02484042212409873</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6168139696338479</v>
+        <v>0.6074203056332033</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05072303073723201</v>
+        <v>0.05134099456476739</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.8455350749967376</v>
+        <v>0.79965696784866</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.004700585775864934</v>
+        <v>0.005353331850964674</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5039501493547531</v>
+        <v>0.4855156788173879</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01177356860081368</v>
+        <v>0.01199034083442036</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4013347893632664</v>
+        <v>0.3986558921977765</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01681330175749516</v>
+        <v>0.01685087770143491</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9895115398216148</v>
+        <v>0.989890950131731</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003545516649194897</v>
+        <v>0.0003480798089429281</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3483,25 +3483,25 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5374259014890495</v>
+        <v>0.5420877920164093</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3599059019324887</v>
+        <v>0.5228421539505494</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.282902876970244</v>
+        <v>4.322202820865563</v>
       </c>
       <c r="P29" t="n">
-        <v>4.206241362661623</v>
+        <v>4.26841435734157</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9366852314083038</v>
+        <v>0.9368370522948155</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01623755293340796</v>
+        <v>0.01621807343019099</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7220543066191655</v>
+        <v>0.7194497357565821</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03435513193226034</v>
+        <v>0.03451572392587886</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9118205146818732</v>
+        <v>0.9322087765903235</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.01028544117865461</v>
+        <v>0.009018324966490665</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.5783721282856094</v>
+        <v>0.6120963091810369</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.009177687338251372</v>
+        <v>0.008802997012286923</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9841052831601101</v>
+        <v>0.9578548773243725</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.003275769347948588</v>
+        <v>0.005334092926115327</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9107411282913163</v>
+        <v>0.9361175600516372</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001783019242800507</v>
+        <v>0.001508415828151936</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3589,25 +3589,25 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4720730841162494</v>
+        <v>0.4777226216200164</v>
       </c>
       <c r="L30" t="n">
-        <v>0.405421165090822</v>
+        <v>0.4494019322425847</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.562326845844513</v>
+        <v>4.562125443659149</v>
       </c>
       <c r="P30" t="n">
-        <v>4.311808835799374</v>
+        <v>4.319516723224595</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.974574664470278</v>
+        <v>0.9743633505822664</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01314314306267128</v>
+        <v>0.01319764739365211</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8803853003666599</v>
+        <v>0.8777572247560574</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02355788118694438</v>
+        <v>0.02381527224812078</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9774394151432966</v>
+        <v>0.9767581143805237</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0006768735906511553</v>
+        <v>0.0006870179473960665</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>-0.0598327692119871</v>
+        <v>-0.07322955449140056</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01392230525653433</v>
+        <v>0.01401002124268474</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8455198730648406</v>
+        <v>0.8631204339067685</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008226413164469575</v>
+        <v>0.00774361084628732</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4721200216573848</v>
+        <v>0.4887902615201305</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001954019775240407</v>
+        <v>0.001922918670333915</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3695,25 +3695,25 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4939662194456111</v>
+        <v>0.4787482540209079</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4302221753435271</v>
+        <v>0.4350374437791852</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.280086717342922</v>
+        <v>4.278628979684508</v>
       </c>
       <c r="P31" t="n">
-        <v>4.391843893111419</v>
+        <v>4.3906308368483</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9843425949262706</v>
+        <v>0.9843946560277957</v>
       </c>
       <c r="R31" t="n">
-        <v>0.008171777066008253</v>
+        <v>0.008158180116866566</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9354362236608754</v>
+        <v>0.9373813819891024</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01357161883866285</v>
+        <v>0.01336561450080574</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.9153744453987112</v>
+        <v>0.9115688666133593</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007082263458684884</v>
+        <v>0.007239755679975879</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.08004122772935918</v>
+        <v>-0.1099505828282106</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009449635265128218</v>
+        <v>0.009579585177555253</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9776912208910113</v>
+        <v>0.9772456841705853</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002343730572965135</v>
+        <v>0.002367018612840365</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.02109647890011457</v>
+        <v>0.01177099596697084</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004158526513618752</v>
+        <v>0.004178287579279344</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3801,25 +3801,25 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5041910255103661</v>
+        <v>0.4809602673783849</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4272514680364557</v>
+        <v>0.4335655740116521</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.563241224115946</v>
+        <v>4.566585713233426</v>
       </c>
       <c r="P32" t="n">
-        <v>4.417668249325046</v>
+        <v>4.416116957587726</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9801322792381413</v>
+        <v>0.9800842773170313</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0135727537514664</v>
+        <v>0.01358914026153745</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.9186604828168569</v>
+        <v>0.9038016562366729</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.008134040418942189</v>
+        <v>0.008845845065414819</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2235580084396153</v>
+        <v>0.2205038059932694</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01749089496889964</v>
+        <v>0.01752526223541849</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.5553005073651391</v>
+        <v>-0.5640594767843738</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01585985253824754</v>
+        <v>0.01590444875870164</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2554367786861873</v>
+        <v>0.2839378366575663</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01787894403175592</v>
+        <v>0.0175334119988577</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.07620075321996744</v>
+        <v>0.08136868300804356</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004885442714179641</v>
+        <v>0.00487175846273836</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3905,25 +3905,25 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2828125477845588</v>
+        <v>0.2241840487608926</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2943407216269099</v>
+        <v>0.2571543585739079</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.275571175206728</v>
+        <v>4.264159583875831</v>
       </c>
       <c r="P33" t="n">
-        <v>4.266016694531364</v>
+        <v>4.255169955041236</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9643692358022204</v>
+        <v>0.9626567925433538</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005988436799279399</v>
+        <v>0.006130652649765775</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9254577824922631</v>
+        <v>0.9235817124416643</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01103263381372728</v>
+        <v>0.01117060513442924</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.09788660787930459</v>
+        <v>-0.02430732550753834</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006095251385106984</v>
+        <v>0.006494955707144202</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8974986867492309</v>
+        <v>0.8896140662631168</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.003818847603978114</v>
+        <v>0.003963003720993876</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7673254880507041</v>
+        <v>0.7922385159223713</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002288793584340332</v>
+        <v>0.002162791923822649</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3722924463802223</v>
+        <v>0.4122211304803141</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007833294870260849</v>
+        <v>0.0007580062367388244</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4009,25 +4009,25 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5387040856238987</v>
+        <v>0.5349473716287773</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4505244806061678</v>
+        <v>0.5381953007689939</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.291280449636701</v>
+        <v>4.267183287460422</v>
       </c>
       <c r="P34" t="n">
-        <v>4.281402786162578</v>
+        <v>4.311846924850413</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8632025530430495</v>
+        <v>0.9349518907930654</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02579236167805296</v>
+        <v>0.01778563816532134</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.7748859956775074</v>
+        <v>0.8953100680352519</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.05679797340671861</v>
+        <v>0.0387332592145739</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9938226148081223</v>
+        <v>0.9956792830090018</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001859203414570875</v>
+        <v>0.001554900051533438</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.5878152494809181</v>
+        <v>0.6997684013904919</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004942525917212037</v>
+        <v>0.004218239137143498</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4122539526376154</v>
+        <v>0.5042044899034201</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.00851009212803502</v>
+        <v>0.007816110635274572</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.1776844239965625</v>
+        <v>0.2795544081821547</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0008815401718817203</v>
+        <v>0.0008251320176955639</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4115,25 +4115,25 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3025718444011018</v>
+        <v>0.2459581993328201</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2499379673751634</v>
+        <v>0.2357202900920975</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.05737490915139</v>
+        <v>3.975752990096821</v>
       </c>
       <c r="P35" t="n">
-        <v>4.15103321646585</v>
+        <v>4.146392989298806</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9970166090418883</v>
+        <v>0.9967487231358749</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005441380135174591</v>
+        <v>0.005680426686592891</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9897875062409014</v>
+        <v>0.9869734202358961</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.005514553380805504</v>
+        <v>0.00622815833049726</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6186558180004975</v>
+        <v>0.6080173027276381</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.009222366157186327</v>
+        <v>0.009350121349424274</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7113312356780586</v>
+        <v>0.6938205739738527</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002171209181928795</v>
+        <v>0.00223609253272939</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5090415643156302</v>
+        <v>0.4864175925066926</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002379104812129503</v>
+        <v>0.002433303505285716</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4217,25 +4217,25 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.432114221689511</v>
+        <v>0.3970681303962988</v>
       </c>
       <c r="L36" t="n">
-        <v>0.393460572400415</v>
+        <v>0.369139604643216</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.321952334671811</v>
+        <v>4.31291763426113</v>
       </c>
       <c r="P36" t="n">
-        <v>4.315683993496754</v>
+        <v>4.307540971892259</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9838277884668162</v>
+        <v>0.9839682395410302</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01152349972275295</v>
+        <v>0.01147335143645518</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8138287247343752</v>
+        <v>0.8175420240239835</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01875632445640098</v>
+        <v>0.01856832916267395</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.4013374024056481</v>
+        <v>0.3901123973213869</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.007937130078895365</v>
+        <v>0.00801119574449703</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06460173304454087</v>
+        <v>0.05902897648300964</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.0134937430523918</v>
+        <v>0.01353387877843194</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7286972638153408</v>
+        <v>0.7332194822345299</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006102019286247539</v>
+        <v>0.006050949738088506</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1549866676212358</v>
+        <v>0.1421094813055929</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004065053402173327</v>
+        <v>0.004095910036102134</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4323,25 +4323,25 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1035375728459106</v>
+        <v>0.05755759486930409</v>
       </c>
       <c r="L37" t="n">
-        <v>0.117180601009066</v>
+        <v>0.07039615854072333</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.240813110988225</v>
+        <v>4.231556993851775</v>
       </c>
       <c r="P37" t="n">
-        <v>4.271075171498469</v>
+        <v>4.259457241386411</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9931872717709982</v>
+        <v>0.9934008170480521</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005499830453704712</v>
+        <v>0.005412947979858859</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.05207706353987218</v>
+        <v>0.1041746620618317</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004165190760751575</v>
+        <v>0.0004049114440893563</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9961141164805039</v>
+        <v>0.9977471006154892</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.002959610491539008</v>
+        <v>0.002253515590155638</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.4729812322212641</v>
+        <v>-0.4503320341645318</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.0076844399373618</v>
+        <v>0.007625131322590794</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.916852348976366</v>
+        <v>0.9176327870772913</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009383752911239048</v>
+        <v>0.009339610343872949</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9336211192272117</v>
+        <v>0.9290850837277947</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002311492477542115</v>
+        <v>0.002389165956738238</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999993425584421</v>
+        <v>0.9999999332876334</v>
       </c>
       <c r="AM37" t="n">
-        <v>7.981496381906415e-07</v>
+        <v>2.542488029421241e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4431,25 +4431,25 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1433109613706779</v>
+        <v>0.08996212189252457</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1277653508763556</v>
+        <v>0.07850193817822804</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.158873949626578</v>
+        <v>4.142537911135626</v>
       </c>
       <c r="P38" t="n">
-        <v>4.198981036502904</v>
+        <v>4.181534136142735</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9433455976724101</v>
+        <v>0.9439553345973661</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01335571115688277</v>
+        <v>0.01328364702190239</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.4923393625643067</v>
+        <v>0.4949028352228363</v>
       </c>
       <c r="X38" t="n">
-        <v>0.0009339074883222234</v>
+        <v>0.0009315465841851858</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.7351384632276249</v>
+        <v>0.7370644446848114</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02482221115691726</v>
+        <v>0.02473179726650826</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.4802497584636272</v>
+        <v>-0.4634348399402461</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01765889697451369</v>
+        <v>0.01755831186386165</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9953271921121237</v>
+        <v>0.9956533553488608</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.001586766861866279</v>
+        <v>0.00153038684759478</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-0.8562212999193628</v>
+        <v>-0.6695256725057415</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004500594301272279</v>
+        <v>0.004268266893322947</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999998041380312</v>
+        <v>0.9999999555727754</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.773751209348075e-07</v>
+        <v>8.447773285118594e-08</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4539,25 +4539,25 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1521632323991432</v>
+        <v>0.09663475671709176</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1365513573779804</v>
+        <v>0.08939318931531109</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.276604215929122</v>
+        <v>4.263201611065282</v>
       </c>
       <c r="P39" t="n">
-        <v>4.264388068889255</v>
+        <v>4.252804447967554</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9816268711025765</v>
+        <v>0.9817165080072754</v>
       </c>
       <c r="R39" t="n">
-        <v>0.009072906735574798</v>
+        <v>0.009050747699988725</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8558176425002724</v>
+        <v>0.8570025677208115</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01270887839098529</v>
+        <v>0.01265654834642219</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1427950472409598</v>
+        <v>0.09250439806797017</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001377447141840691</v>
+        <v>0.001417277429345569</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.04672596509918936</v>
+        <v>-0.04433177105226305</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01465421133600714</v>
+        <v>0.01463744232896824</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7564767927545104</v>
+        <v>0.758832661452113</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005355018402313135</v>
+        <v>0.005329052949697349</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1164566034893098</v>
+        <v>-0.1109729504455579</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002180160683826378</v>
+        <v>0.002174799993712583</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4643,25 +4643,25 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.249459596754826</v>
+        <v>0.2447240331807525</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4060580165575136</v>
+        <v>0.3951933466404473</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.314959883928858</v>
+        <v>4.317329227224308</v>
       </c>
       <c r="P40" t="n">
-        <v>4.519929776461174</v>
+        <v>4.521128601863206</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9938311116255427</v>
+        <v>0.9936156828640696</v>
       </c>
       <c r="R40" t="n">
-        <v>0.004717843391356832</v>
+        <v>0.004799514306155445</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9797354819774584</v>
+        <v>0.9787813874118515</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.008590725492072768</v>
+        <v>0.008790633913835924</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9638233453426077</v>
+        <v>0.9615914485345455</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0004327097056782412</v>
+        <v>0.0004458578307968994</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9826533438533495</v>
+        <v>0.9818392359460656</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.00330819565323594</v>
+        <v>0.003384935203069438</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.992448641969473</v>
+        <v>0.9926975806318903</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.003902466848552621</v>
+        <v>0.003837603280255175</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999997809895194</v>
+        <v>0.9999999486643067</v>
       </c>
       <c r="AM40" t="n">
-        <v>2.84547108624948e-07</v>
+        <v>1.377626342413024e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4747,25 +4747,25 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2573692229621695</v>
+        <v>0.195223836174422</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2816395327127157</v>
+        <v>0.2298258348825929</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.427001742671981</v>
+        <v>4.426831872784585</v>
       </c>
       <c r="P41" t="n">
-        <v>4.51040769462028</v>
+        <v>4.510621737373024</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9936862574154206</v>
+        <v>0.9937137837198757</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006158265972016336</v>
+        <v>0.006144827076517603</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8714355505963176</v>
+        <v>0.8728325443674019</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.0104416148351391</v>
+        <v>0.01038473008392041</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.5896632588938575</v>
+        <v>0.5254581666673552</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001597506265128528</v>
+        <v>0.001717946438608115</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9693153147744089</v>
+        <v>0.9690231914527679</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.004696795997337061</v>
+        <v>0.004719100179292481</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9471342693856056</v>
+        <v>0.9472947983777226</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007412723154435572</v>
+        <v>0.007401460077657572</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.9028596321955266</v>
+        <v>0.9107994017799814</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001016609597162556</v>
+        <v>0.0009741777745125676</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4851,25 +4851,25 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3161275944552756</v>
+        <v>0.1311334681965219</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4155201972372792</v>
+        <v>0.3643118556996269</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.505860970347477</v>
+        <v>2.432463726727812</v>
       </c>
       <c r="P42" t="n">
-        <v>4.560499203060885</v>
+        <v>4.446764941811143</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9665756487176985</v>
+        <v>0.9664345598777271</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01210684093748995</v>
+        <v>0.01213236636094017</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8849506236851598</v>
+        <v>0.8849287038513132</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.01861377024741266</v>
+        <v>0.01861554336026069</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9636443743332248</v>
+        <v>0.9074499484805287</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.00101909861271533</v>
+        <v>0.001625993223408512</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6756110582638586</v>
+        <v>0.6720922251522206</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01662264377356529</v>
+        <v>0.01671255828538804</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9881447871972849</v>
+        <v>0.9902230400385768</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.003367139974697419</v>
+        <v>0.003057795322369573</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4953,25 +4953,25 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2145613387877751</v>
+        <v>0.1864807199699899</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3889771463935804</v>
+        <v>0.3813980592219544</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.957269318509153</v>
+        <v>3.965151146825701</v>
       </c>
       <c r="P43" t="n">
-        <v>4.261918923283186</v>
+        <v>4.255277474965847</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9613909978500171</v>
+        <v>0.9637435824330903</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01200591943751869</v>
+        <v>0.01163438901603885</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9359512872315633</v>
+        <v>0.9419862676144334</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02176503272872378</v>
+        <v>0.02071426486500939</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.8520911198452248</v>
+        <v>0.9290813733079974</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.001816270227262488</v>
+        <v>0.001257660722955492</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.759371440608578</v>
+        <v>0.7572337246815359</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01554544951738278</v>
+        <v>0.01561434883609222</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.9435768883116423</v>
+        <v>0.9345506253759777</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001331565908907165</v>
+        <v>0.001434124652390169</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9834767256382397</v>
+        <v>0.983033213530069</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0005108346237562572</v>
+        <v>0.0005176450492680529</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5057,25 +5057,25 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1729821644702371</v>
+        <v>0.1160040171888872</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3955313657661261</v>
+        <v>0.3735129748774897</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.220618689085988</v>
+        <v>4.221992695387505</v>
       </c>
       <c r="P44" t="n">
-        <v>4.392844010909901</v>
+        <v>4.382485131575057</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9519845256476372</v>
+        <v>0.9497680203236549</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007463494940070896</v>
+        <v>0.007633817587803252</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9586228785039925</v>
+        <v>0.9586852425575962</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.009121711403111717</v>
+        <v>0.009114834642967263</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.9455523891613016</v>
+        <v>0.9617882175303062</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.002587860918124825</v>
+        <v>0.002167954516308869</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9038505559368722</v>
+        <v>0.9005731097004525</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01084517779808726</v>
+        <v>0.01102846872531767</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8524112247880553</v>
+        <v>0.8289534223201793</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.008345871343629836</v>
+        <v>0.008984671754363656</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.7002634934257979</v>
+        <v>0.7226702336537871</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001159607947780862</v>
+        <v>0.001115423017012463</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5161,25 +5161,25 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.402064738426252</v>
+        <v>0.3599855396326003</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3475688637037856</v>
+        <v>0.4780692681106861</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.273822963139304</v>
+        <v>4.246879291334123</v>
       </c>
       <c r="P45" t="n">
-        <v>4.371840953772796</v>
+        <v>4.417093918109077</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9658466124528553</v>
+        <v>0.9708105449849361</v>
       </c>
       <c r="R45" t="n">
-        <v>0.009025618827383747</v>
+        <v>0.008343976808991141</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9717844804701022</v>
+        <v>0.977623974881089</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01436720995678839</v>
+        <v>0.01279439878471158</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9214806880545869</v>
+        <v>0.9267256335999999</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007349009306114705</v>
+        <v>0.007099317356187763</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8704565050127979</v>
+        <v>0.8803907494121218</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008553132260802921</v>
+        <v>0.008218636411868164</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9208076557519436</v>
+        <v>0.9285937569966096</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008563938286751661</v>
+        <v>0.008132049650928045</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9799171581444163</v>
+        <v>0.9825428328570887</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006222587180918955</v>
+        <v>0.0005801566712257643</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5265,25 +5265,25 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4152342674066459</v>
+        <v>0.4033453330186448</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3807848635863</v>
+        <v>0.4827793077555627</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.736658907187545</v>
+        <v>3.778791310898719</v>
       </c>
       <c r="P46" t="n">
-        <v>4.48946306585675</v>
+        <v>4.471113017760768</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9615264294618416</v>
+        <v>0.970942414317038</v>
       </c>
       <c r="R46" t="n">
-        <v>0.009352063529390156</v>
+        <v>0.008127481051106738</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9776538414275411</v>
+        <v>0.9843011732410716</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01152696281645199</v>
+        <v>0.009661555494740289</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9041293457485774</v>
+        <v>0.921445909643171</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01149278919874865</v>
+        <v>0.01040320118583147</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9787268952371752</v>
+        <v>0.9887377640675967</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002387503331102444</v>
+        <v>0.001737164144234148</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8489309668734064</v>
+        <v>0.8862086480992423</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01287106542646347</v>
+        <v>0.01117072606139732</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9867838400593032</v>
+        <v>0.9878731153740746</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009929192221314999</v>
+        <v>0.0009511212787388205</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5369,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.249759804799666</v>
+        <v>0.1903563654068834</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4061826014847641</v>
+        <v>0.383825374248957</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.226749871470481</v>
+        <v>4.218169191500397</v>
       </c>
       <c r="P47" t="n">
-        <v>4.357803244108987</v>
+        <v>4.348032416494451</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9589125222689501</v>
+        <v>0.9599347168078145</v>
       </c>
       <c r="R47" t="n">
-        <v>0.007617541328697981</v>
+        <v>0.007522188055672782</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9576731773183128</v>
+        <v>0.9582549409130878</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01133573204915898</v>
+        <v>0.01125756017980058</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.9063341516565808</v>
+        <v>0.9258573659303182</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.004781956926118184</v>
+        <v>0.004254504917568309</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8520133906469718</v>
+        <v>0.8516816592404678</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01147008524573142</v>
+        <v>0.01148293389811186</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9713339561655905</v>
+        <v>0.9753962119561104</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.002625703281329063</v>
+        <v>0.002432555488606362</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9146403158551536</v>
+        <v>0.9156204911697772</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005581873096024894</v>
+        <v>0.0005549732565910903</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5473,25 +5473,25 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.112812893274769</v>
+        <v>0.06980095781629543</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4712448926497022</v>
+        <v>0.4891965550851729</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.689594567822128</v>
+        <v>3.762510994332883</v>
       </c>
       <c r="P48" t="n">
-        <v>4.332382146406159</v>
+        <v>4.335389356787959</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9942150638287417</v>
+        <v>0.9934909134209663</v>
       </c>
       <c r="R48" t="n">
-        <v>0.003921728189367217</v>
+        <v>0.004159951126299398</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9963374720407574</v>
+        <v>0.9969887998179667</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.004425228507921046</v>
+        <v>0.004012499959619337</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.9455904102927983</v>
+        <v>0.9515437868510984</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.003940298040925931</v>
+        <v>0.003718485418227059</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9886933385846548</v>
+        <v>0.9845365094001055</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.006166338720971824</v>
+        <v>0.007211306441372915</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.9449305151071618</v>
+        <v>0.9328221047545728</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.001939244453785518</v>
+        <v>0.002141855890942622</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9998872132943413</v>
+        <v>0.9998633905181861</v>
       </c>
       <c r="AM48" t="n">
-        <v>8.222946218451477e-05</v>
+        <v>9.049798635107402e-05</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5577,25 +5577,25 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3620994881251263</v>
+        <v>0.3226065171575305</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4637656770311649</v>
+        <v>0.4679601386457435</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.033112792883243</v>
+        <v>4.046686012503025</v>
       </c>
       <c r="P49" t="n">
-        <v>4.394942862891178</v>
+        <v>4.392929282742907</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9330972743352871</v>
+        <v>0.9388380743525918</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01226018952121035</v>
+        <v>0.01172238155085329</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9450246457949445</v>
+        <v>0.951601449545898</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01581564234444936</v>
+        <v>0.01483949064995612</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9489030406969238</v>
+        <v>0.9432058990801755</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002167741049540636</v>
+        <v>0.002285396130729579</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4369628064539961</v>
+        <v>0.4468575744822459</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01385299363521287</v>
+        <v>0.01373072839791452</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3721399672767072</v>
+        <v>0.4377053357995841</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01740971013083599</v>
+        <v>0.01647563273790522</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8708018801775679</v>
+        <v>0.8757400885660562</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001313069669741915</v>
+        <v>0.001287731122093818</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5681,25 +5681,25 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5100697585861687</v>
+        <v>0.4990340157055358</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5534890747704226</v>
+        <v>0.5570377646805023</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.291959939524077</v>
+        <v>4.286590071874298</v>
       </c>
       <c r="P50" t="n">
-        <v>4.517901989223707</v>
+        <v>4.454399903699594</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9646581004431101</v>
+        <v>0.9655650127546536</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01004792749893568</v>
+        <v>0.009918169177730881</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9852643325071451</v>
+        <v>0.9853576474094458</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01021240998622435</v>
+        <v>0.01018002314454023</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9385400938770382</v>
+        <v>0.9409967881670245</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005282459760951425</v>
+        <v>0.00517580704938125</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.949613260751951</v>
+        <v>0.9504931933453787</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002293351044626732</v>
+        <v>0.002273237784152495</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8189356378143295</v>
+        <v>0.8246123617624693</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01707707357789213</v>
+        <v>0.01680724187523902</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5783,25 +5783,25 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4766078924922043</v>
+        <v>0.4747357510883822</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5516876227432732</v>
+        <v>0.5579599798746322</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.851203782657342</v>
+        <v>3.849426342197498</v>
       </c>
       <c r="P51" t="n">
-        <v>4.424936364643755</v>
+        <v>4.425587969768034</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9284394557088755</v>
+        <v>0.9284913565194352</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01074361698339259</v>
+        <v>0.01073972025909145</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9297049037140779</v>
+        <v>0.9294386476056465</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01567476265628154</v>
+        <v>0.01570442019597428</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7956633511931013</v>
+        <v>0.7969528645570624</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01443360908798849</v>
+        <v>0.01438799370452885</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8076971065108969</v>
+        <v>-0.8038817080187282</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003372865476808775</v>
+        <v>0.003369304156913873</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8919091967836299</v>
+        <v>0.8919183321684983</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01055573125576267</v>
+        <v>0.01055528515928503</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9956305534453201</v>
+        <v>0.995646094024108</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005473480839950982</v>
+        <v>0.0005463738544171479</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5887,25 +5887,25 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1562936953832578</v>
+        <v>0.1003996704124989</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2432115949197743</v>
+        <v>0.1777223013219234</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.255272484088167</v>
+        <v>4.241864768630935</v>
       </c>
       <c r="P52" t="n">
-        <v>4.298583021057969</v>
+        <v>4.281831274105524</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9525945332370921</v>
+        <v>0.950738776287964</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0105139880429486</v>
+        <v>0.0107178052978113</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9660857974002085</v>
+        <v>0.9655547306740604</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.008433082707538257</v>
+        <v>0.008498853573057788</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.773926547449727</v>
+        <v>0.7626227056864362</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.003363550091334485</v>
+        <v>0.003446614446363295</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7692294411896498</v>
+        <v>0.758369132571489</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01725006129873364</v>
+        <v>0.01765129805805236</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.367799419229467</v>
+        <v>0.3459944916243263</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01310851270697796</v>
+        <v>0.01333265613695981</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.04072390418856464</v>
+        <v>0.01124947048461</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009442719249044745</v>
+        <v>0.0009586688741098741</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -5991,25 +5991,25 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3358214977156688</v>
+        <v>0.2783551458295477</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2369894245726382</v>
+        <v>0.2437999890170973</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.452334897594409</v>
+        <v>4.435198931413451</v>
       </c>
       <c r="P53" t="n">
-        <v>4.414200628330695</v>
+        <v>4.415506837896285</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9798716509251806</v>
+        <v>0.9804376121938031</v>
       </c>
       <c r="R53" t="n">
-        <v>0.006099820686040818</v>
+        <v>0.006013453024760021</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.965172350531748</v>
+        <v>0.9624050616294558</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.01081574464545895</v>
+        <v>0.01123722383391647</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.810031119866949</v>
+        <v>0.870693185504316</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.00447425700144224</v>
+        <v>0.003691393996139574</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9845986835733542</v>
+        <v>0.9839342787485116</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003063915831139631</v>
+        <v>0.003129305922309538</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9642202717139952</v>
+        <v>0.973984025780773</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005508477841410778</v>
+        <v>0.004697135996622727</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9531433687948713</v>
+        <v>0.9289542255235578</v>
       </c>
       <c r="AM53" t="n">
-        <v>9.586524183558239e-05</v>
+        <v>0.0001180442305928205</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6095,25 +6095,25 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2232363824600347</v>
+        <v>0.1652005085621645</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4375264112632372</v>
+        <v>0.4241892678845949</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.144200181763916</v>
+        <v>4.147708344073651</v>
       </c>
       <c r="P54" t="n">
-        <v>4.316533435116456</v>
+        <v>4.30350884959747</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9366030132557153</v>
+        <v>0.9345179638454467</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009142934786936875</v>
+        <v>0.009292068476935143</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.9261015759168229</v>
+        <v>0.9274567953518621</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.014005817333021</v>
+        <v>0.01387679707642824</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.7887358602280492</v>
+        <v>0.8725747593107307</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.00265066471531907</v>
+        <v>0.002058588941304342</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8036608566898976</v>
+        <v>0.7970722274971908</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01314074700920427</v>
+        <v>0.01335941229666852</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.7507807586900389</v>
+        <v>0.6630659026654788</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.0063968788415862</v>
+        <v>0.007437891239724197</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8642805433697253</v>
+        <v>0.8717430454111224</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001085379711469188</v>
+        <v>0.001055118175507888</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6199,25 +6199,25 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.196852432134677</v>
+        <v>0.1364807019502954</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4676882240271638</v>
+        <v>0.4768399884928943</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.361472218356489</v>
+        <v>4.361516370208551</v>
       </c>
       <c r="P55" t="n">
-        <v>4.402559510476355</v>
+        <v>4.403259184616267</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8850052417179333</v>
+        <v>0.8786969627940339</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01367465153775916</v>
+        <v>0.01404471993814226</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.8321391607880551</v>
+        <v>0.8379112565364591</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.01977699441235166</v>
+        <v>0.01943399217449959</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.5594442934092601</v>
+        <v>0.6568116185794668</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.002906178200845838</v>
+        <v>0.00256500439447723</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.5156977542095719</v>
+        <v>0.4460682610721654</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.02229181478895856</v>
+        <v>0.02384049726286353</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8128425269219781</v>
+        <v>0.8366148079347332</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.00617900053257729</v>
+        <v>0.00577325836138806</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8436896170382504</v>
+        <v>0.8376307997933843</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.000547758621669043</v>
+        <v>0.0005582736552216432</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6303,25 +6303,25 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2062853367551514</v>
+        <v>0.150223218442535</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3886907981446448</v>
+        <v>0.3802329027483022</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.024244761351999</v>
+        <v>4.031079539857037</v>
       </c>
       <c r="P56" t="n">
-        <v>4.335874724164384</v>
+        <v>4.329513765345777</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8545500202619801</v>
+        <v>0.8588250748292413</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01119003320147255</v>
+        <v>0.01102435845152604</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.7533589873120485</v>
+        <v>0.7643505488262843</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.01733924711215762</v>
+        <v>0.01694848192806018</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>0.3262060422775743</v>
+        <v>0.414535291790888</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.007194331888172362</v>
+        <v>0.006706211918995282</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6484351885282893</v>
+        <v>0.6369819916521644</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01567625327655565</v>
+        <v>0.01592955549241604</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8803928136720532</v>
+        <v>0.9099469525302347</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005028178966376814</v>
+        <v>0.004362960661145289</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8821250911036076</v>
+        <v>0.8810970529064113</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.00162751743708451</v>
+        <v>0.001634599172197314</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6407,25 +6407,25 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3797827501136171</v>
+        <v>0.336114860226541</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4582444120870413</v>
+        <v>0.4549878851690105</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.247766393668665</v>
+        <v>4.246456518302081</v>
       </c>
       <c r="P57" t="n">
-        <v>4.37449370847799</v>
+        <v>4.37118239374384</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9121614084768805</v>
+        <v>0.9174033747813065</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009012323331070929</v>
+        <v>0.008739271548761043</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.8132962131565457</v>
+        <v>0.8225089339754295</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01635462927421844</v>
+        <v>0.01594602311924009</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.7126983537525658</v>
+        <v>0.7460590362564933</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.007727322413732051</v>
+        <v>0.007264845079473673</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7475439468977283</v>
+        <v>0.7545560697554174</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007713494517266502</v>
+        <v>0.007605616595456919</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9472210032347024</v>
+        <v>0.9540590701503557</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004227745852606556</v>
+        <v>0.003944375005483938</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6892384405335991</v>
+        <v>0.7163403052433504</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001246040157381087</v>
+        <v>0.00119046658325743</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6511,25 +6511,25 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2024072301870911</v>
+        <v>0.1666120314608137</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5061444885241897</v>
+        <v>0.5078008476146383</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.10470435677508</v>
+        <v>4.116850885198406</v>
       </c>
       <c r="P58" t="n">
-        <v>4.417317337476732</v>
+        <v>4.417779893902977</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.969779090938868</v>
+        <v>0.9660242797525445</v>
       </c>
       <c r="R58" t="n">
-        <v>0.007310111744225025</v>
+        <v>0.007750943831651662</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9894655837610564</v>
+        <v>0.9896642064324948</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.005955296625892809</v>
+        <v>0.005898886966643586</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9867414870619635</v>
+        <v>0.9968835627317832</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001059750031214271</v>
+        <v>0.0005137894996150943</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9758403265398836</v>
+        <v>0.9645349622691615</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.005972271584169496</v>
+        <v>0.00723592791542719</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.7047337141015073</v>
+        <v>0.6773351450680378</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01394039757509405</v>
+        <v>0.01457283544935341</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9523788416415666</v>
+        <v>0.9522759688193978</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0007728700456659487</v>
+        <v>0.0007737043884796557</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6615,25 +6615,25 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4652114978160279</v>
+        <v>0.4445932488388378</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5157910151339415</v>
+        <v>0.5303639586495459</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.189896485281355</v>
+        <v>4.18553294972197</v>
       </c>
       <c r="P59" t="n">
-        <v>4.384984725234256</v>
+        <v>4.386081743854972</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.8090252100858104</v>
+        <v>0.8240364891046514</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0187053106076517</v>
+        <v>0.01795511590985745</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7850738976500554</v>
+        <v>0.8056986903930172</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.02906272834793005</v>
+        <v>0.02763310359241945</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4681752040379594</v>
+        <v>0.5017130496640901</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02253686245002089</v>
+        <v>0.02181468367025187</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1413049826947327</v>
+        <v>0.1372582130778718</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01075036147511836</v>
+        <v>0.01077566327015386</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.7873784136543076</v>
+        <v>-0.6270350616377951</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01658349341908137</v>
+        <v>0.01582217648112993</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5568262532607748</v>
+        <v>-0.4821878074174244</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002511643028074254</v>
+        <v>0.002450696102697557</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6719,25 +6719,25 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3216419994495925</v>
+        <v>0.271635444752685</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2754641114172093</v>
+        <v>0.2197493253536007</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.066724723170381</v>
+        <v>4.049738163537739</v>
       </c>
       <c r="P60" t="n">
-        <v>4.195073298832094</v>
+        <v>4.172257271912598</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8116662969327862</v>
+        <v>0.8435759017928121</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02699209329262224</v>
+        <v>0.02459939201145507</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.2883718764323214</v>
+        <v>0.4126446638066832</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.05910067901708698</v>
+        <v>0.05369284031156508</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.657799549627808</v>
+        <v>-1.631543459978086</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008640415131379848</v>
+        <v>0.008597630379504898</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6223239458253429</v>
+        <v>0.6514813785434621</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.00677754268735502</v>
+        <v>0.006510667696316503</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-4.89634677206556</v>
+        <v>-4.295705809510738</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.005402902226488513</v>
+        <v>0.005120325009296735</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9490885277054169</v>
+        <v>0.9460302307768018</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004382126388825029</v>
+        <v>0.0004511826101428157</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6823,25 +6823,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.354482847122061</v>
+        <v>0.2900866812720037</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3236217673834675</v>
+        <v>0.3235930351598962</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.865370088861562</v>
+        <v>3.873303134771478</v>
       </c>
       <c r="P61" t="n">
-        <v>4.231305426933169</v>
+        <v>4.241229327374008</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9447594290620249</v>
+        <v>0.9897319443067196</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01675691354403788</v>
+        <v>0.00722452099451669</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.8932288557403374</v>
+        <v>0.9844462450436767</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.03641693107707326</v>
+        <v>0.01389933498608715</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.01951775498147301</v>
+        <v>0.08857685966270845</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.005367646419100328</v>
+        <v>0.005175163240744024</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6555672291491994</v>
+        <v>0.7046601507683745</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005946318360254478</v>
+        <v>0.005506262982388584</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.8559920197379396</v>
+        <v>0.9023526676581937</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.003033397366743239</v>
+        <v>0.002497849214080835</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.2578341800362859</v>
+        <v>0.2527053059078003</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002346822008842813</v>
+        <v>0.002354917103036902</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6929,25 +6929,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.08024552226375803</v>
+        <v>0.09212125147723838</v>
       </c>
       <c r="L62" t="n">
-        <v>0.1381339878187344</v>
+        <v>0.1893108692680267</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.141186837809406</v>
+        <v>4.146801828112358</v>
       </c>
       <c r="P62" t="n">
-        <v>4.162196773361142</v>
+        <v>4.175812232283768</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9891079826175364</v>
+        <v>0.989519187825648</v>
       </c>
       <c r="R62" t="n">
-        <v>0.006882907445634039</v>
+        <v>0.006751732630361767</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9844337879164503</v>
+        <v>0.9848994465622071</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01301346059979336</v>
+        <v>0.01281733579105725</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.1401515107108542</v>
+        <v>-0.01178051016461801</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003554667780729094</v>
+        <v>0.003348581613478699</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.7502087479029408</v>
+        <v>0.7542340609830555</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.006691626339132252</v>
+        <v>0.006637490553611247</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9686188992059851</v>
+        <v>0.9755394258335036</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002629903509816402</v>
+        <v>0.002321876154131657</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8410207675549884</v>
+        <v>0.851331357884626</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001997498178529089</v>
+        <v>0.001931638628279937</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7035,25 +7035,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2554525714322202</v>
+        <v>0.245877187307462</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2862074082137656</v>
+        <v>0.3130009927975516</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.980842593650126</v>
+        <v>3.984786969934592</v>
       </c>
       <c r="P63" t="n">
-        <v>4.217261579853127</v>
+        <v>4.224322691399065</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9827688126286818</v>
+        <v>0.9927600276821922</v>
       </c>
       <c r="R63" t="n">
-        <v>0.009600898609111327</v>
+        <v>0.006223328610771743</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9649717576232076</v>
+        <v>0.9863949147179949</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.02060862048660414</v>
+        <v>0.01284370680025311</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.7203217739104339</v>
+        <v>0.7846206735627993</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.002309265551940402</v>
+        <v>0.002026499747093262</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9672409336188823</v>
+        <v>0.9763553638295647</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.002012937104873775</v>
+        <v>0.001710136457959578</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.7036672958122212</v>
+        <v>0.7663972237909493</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.00485480072176</v>
+        <v>0.00431043019449963</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.2459152511012133</v>
+        <v>0.2787534016134698</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002005404861163218</v>
+        <v>0.001961254135087163</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7141,25 +7141,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1997197132401451</v>
+        <v>0.2058383658046032</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2892619500463863</v>
+        <v>0.3276692405796741</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.711467818595111</v>
+        <v>3.788363809657385</v>
       </c>
       <c r="P64" t="n">
-        <v>4.226872715202777</v>
+        <v>4.240965440942642</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9767762504767393</v>
+        <v>0.9845331187303632</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01021049506228999</v>
+        <v>0.008332628237784316</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9635346399040459</v>
+        <v>0.9780866819727823</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.02016733788819036</v>
+        <v>0.01563372225781761</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.3035166962356732</v>
+        <v>0.4281534413562812</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.004506990812565222</v>
+        <v>0.004083862166227547</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.4384643318008835</v>
+        <v>0.4826411336015208</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.009118562377234187</v>
+        <v>0.008752530795127833</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9673876908292794</v>
+        <v>0.9748136349059898</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002606296717787316</v>
+        <v>0.002290423700010422</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.831947140194401</v>
+        <v>0.8349271527038407</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.0023172184283091</v>
+        <v>0.002296581392267108</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7247,25 +7247,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3034647984070029</v>
+        <v>0.2883423509517015</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3724942244605007</v>
+        <v>0.397450160189017</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.907603328633307</v>
+        <v>3.920690783523073</v>
       </c>
       <c r="P65" t="n">
-        <v>4.260244269585109</v>
+        <v>4.269342147129069</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9718564603301845</v>
+        <v>0.9809556922245833</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01208376152318062</v>
+        <v>0.009940205940611284</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9514031216366629</v>
+        <v>0.9688783463296606</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02520226591933868</v>
+        <v>0.02016818125867519</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6561951676162501</v>
+        <v>0.6881461167889832</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003970445056921395</v>
+        <v>0.003781453628702049</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6587521909123003</v>
+        <v>0.6830375560113259</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008222238418852921</v>
+        <v>0.007924265781863463</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.8832292466624121</v>
+        <v>0.9006434834354127</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002948286532865155</v>
+        <v>0.002719573663082248</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5606336110063638</v>
+        <v>0.5723820649757536</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001894143351912501</v>
+        <v>0.001868647502030359</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7353,25 +7353,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2512712524681031</v>
+        <v>0.2456395141532432</v>
       </c>
       <c r="L66" t="n">
-        <v>0.303987838451985</v>
+        <v>0.3373278288439179</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.955403547984412</v>
+        <v>3.965660158081453</v>
       </c>
       <c r="P66" t="n">
-        <v>4.233530557733366</v>
+        <v>4.246202400898865</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9734023404809052</v>
+        <v>0.983026048890795</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01103100940212961</v>
+        <v>0.008812213632410597</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9549295411090574</v>
+        <v>0.973782073543737</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.0223473903783781</v>
+        <v>0.01704433243298127</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.522246034208256</v>
+        <v>0.6034220206970798</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.004260855409984499</v>
+        <v>0.003882030516074111</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6751432117666203</v>
+        <v>0.7005248052212485</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008708085439359236</v>
+        <v>0.008360979068900359</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9419618121103369</v>
+        <v>0.9529626417229008</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003350583691165243</v>
+        <v>0.003016372755911215</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8450691520827578</v>
+        <v>0.8494051953066842</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002178856784605068</v>
+        <v>0.002148150631739629</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7459,25 +7459,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4211240356731683</v>
+        <v>0.3803330682882993</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3997698344858632</v>
+        <v>0.402064690565567</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.407889787316897</v>
+        <v>4.396081402485587</v>
       </c>
       <c r="P67" t="n">
-        <v>4.345422306408049</v>
+        <v>4.340603481455431</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8525283223387797</v>
+        <v>0.8870173099560962</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02777577468623323</v>
+        <v>0.0243118398107116</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.7848923290825796</v>
+        <v>0.8166418893170564</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0008061945192351184</v>
+        <v>0.0007443238841957515</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.5893867000004429</v>
+        <v>0.6902755728413208</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06602763115315909</v>
+        <v>0.05734518253962988</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7429593583918832</v>
+        <v>0.7804871108164795</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002777554264768829</v>
+        <v>0.002566797851504117</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6313608152100949</v>
+        <v>0.630229902898833</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01331734914401607</v>
+        <v>0.01333776106996026</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8054099352659447</v>
+        <v>0.830338322795523</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.009135539502298827</v>
+        <v>0.008530328278336136</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8374267526895326</v>
+        <v>0.8644145740937728</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001076068417155008</v>
+        <v>9.827020924605216e-05</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7567,25 +7567,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4316687937084649</v>
+        <v>0.3898978456369451</v>
       </c>
       <c r="L68" t="n">
-        <v>0.4166102059554699</v>
+        <v>0.427057669191634</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.511522348131344</v>
+        <v>4.4998735413301</v>
       </c>
       <c r="P68" t="n">
-        <v>4.352269501750476</v>
+        <v>4.348443304872234</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7440927573902089</v>
+        <v>0.7921782683599063</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03374607620841535</v>
+        <v>0.03041077400584544</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.5167933888166578</v>
+        <v>0.590198513143251</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001136792986735699</v>
+        <v>0.001046891603741876</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.3028493435110874</v>
+        <v>0.4367865410735904</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.08121992231825687</v>
+        <v>0.07300216861452564</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.5021183811289898</v>
+        <v>0.579995793361331</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003765720915132895</v>
+        <v>0.003458692116971544</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.691631281567803</v>
+        <v>0.7221168682899132</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.008165950851645492</v>
+        <v>0.007751802472497716</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6985801701883201</v>
+        <v>0.7132144204891897</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01238043913676423</v>
+        <v>0.01207615818490496</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.3341717975594742</v>
+        <v>0.4102490126832622</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007252042009551913</v>
+        <v>0.000682517132152306</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7675,25 +7675,25 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1562554941398337</v>
+        <v>0.1000285343957928</v>
       </c>
       <c r="L69" t="n">
-        <v>0.1861352270848367</v>
+        <v>0.1376482437302084</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.301187016990273</v>
+        <v>4.290484453614669</v>
       </c>
       <c r="P69" t="n">
-        <v>4.304736348181783</v>
+        <v>4.295084257352682</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9673355863360517</v>
+        <v>0.967105567637897</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01059263457012876</v>
+        <v>0.01062986514420284</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9389258171915439</v>
+        <v>0.9390004466290763</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01369120131160974</v>
+        <v>0.01368283379604296</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.3483877229764311</v>
+        <v>0.2823575941037463</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.005126252776728942</v>
+        <v>0.005379717061389629</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8468597089458333</v>
+        <v>0.8468023779719942</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01584670261327996</v>
+        <v>0.01584966859580521</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9159461069000925</v>
+        <v>0.9144219897283106</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.008796645685422454</v>
+        <v>0.008876040498207222</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5061216104844813</v>
+        <v>0.5056048655141325</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004335102740062144</v>
+        <v>0.004337370061025639</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7779,25 +7779,25 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1527928836483235</v>
+        <v>0.09682343377553043</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2675271120949496</v>
+        <v>0.2154705684160599</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.339893559122465</v>
+        <v>4.334140788598515</v>
       </c>
       <c r="P70" t="n">
-        <v>4.373194889845031</v>
+        <v>4.365298204463088</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9515721611432411</v>
+        <v>0.9510531423117994</v>
       </c>
       <c r="R70" t="n">
-        <v>0.01079941589058032</v>
+        <v>0.01085713230234519</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.8520610381033237</v>
+        <v>0.8504141587675277</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01717435689883341</v>
+        <v>0.01726968612861882</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.893309346381268</v>
+        <v>0.8895477830624512</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.00378890398886918</v>
+        <v>0.00385511760345361</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.940221987907637</v>
+        <v>0.9396217655491471</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.0111020237121112</v>
+        <v>0.01115762139290341</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8146333345514486</v>
+        <v>0.8132242170435352</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01205880014581655</v>
+        <v>0.01210454757712278</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7471408191864253</v>
+        <v>0.7413979698556326</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002270021608309901</v>
+        <v>0.002295654861137608</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7883,25 +7883,25 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3251980729523765</v>
+        <v>0.2678404883365064</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3388538564529291</v>
+        <v>0.3051894735492469</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.4265321563301</v>
+        <v>4.421523566309154</v>
       </c>
       <c r="P71" t="n">
-        <v>4.442648558535788</v>
+        <v>4.440366686285005</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9597880614638961</v>
+        <v>0.9589901801271565</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0109492079010399</v>
+        <v>0.01105730089673685</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9398073718015236</v>
+        <v>0.9386565066021952</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01460162932946054</v>
+        <v>0.01474055782117036</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7299603223088129</v>
+        <v>0.7016081158245309</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004603144788583897</v>
+        <v>0.004838762970126784</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9057230426477835</v>
+        <v>0.9039585548816949</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009792808804193242</v>
+        <v>0.00988402508967318</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8403717129968757</v>
+        <v>0.8381954744767918</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01637542490364737</v>
+        <v>0.01648667144988083</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9360775720841192</v>
+        <v>0.9267766087720023</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009877257872836157</v>
+        <v>0.001057145295097156</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -7987,25 +7987,25 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3226988012903637</v>
+        <v>0.2638017802804687</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4017290501323692</v>
+        <v>0.3646089381137353</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.500658295365612</v>
+        <v>4.502235920367876</v>
       </c>
       <c r="P72" t="n">
-        <v>4.513285792519836</v>
+        <v>4.51606662036576</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9522085015583066</v>
+        <v>0.9503965885115232</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01248403989486677</v>
+        <v>0.01271849129849006</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8354727484216882</v>
+        <v>0.8298822118045739</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01694087166883833</v>
+        <v>0.01722628764741622</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.7156760303640204</v>
+        <v>0.6775039541099062</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.005873399196269812</v>
+        <v>0.006255254435713002</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9507472067077319</v>
+        <v>0.9480593937526761</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006954812499250478</v>
+        <v>0.007142060100385534</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8465011975139933</v>
+        <v>0.8417979645072993</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.02018170661824531</v>
+        <v>0.0204885595446248</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.8992003415007763</v>
+        <v>0.8972183578532147</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001447622374680859</v>
+        <v>0.001461785104127979</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8091,25 +8091,25 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08013831924157826</v>
+        <v>0.04031370470886774</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08703404128132332</v>
+        <v>0.05058597310616091</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.345718815687935</v>
+        <v>4.339334217678624</v>
       </c>
       <c r="P73" t="n">
-        <v>4.333874858928858</v>
+        <v>4.329512466514699</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9947699944715903</v>
+        <v>0.9947784054336702</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004809536328713667</v>
+        <v>0.004805667393236851</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9561793796709384</v>
+        <v>0.9564836101284306</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.00718739683744775</v>
+        <v>0.007162403657374774</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6414271255723738</v>
+        <v>0.6670088786214637</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001197029191837482</v>
+        <v>0.001153539186249257</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9730474336871866</v>
+        <v>0.9730948768231139</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.005508252543151468</v>
+        <v>0.005503402464363028</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8218614884701047</v>
+        <v>0.8202753343659046</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005160520620231417</v>
+        <v>0.005183444479077116</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.0748496756734609</v>
+        <v>-0.09236174743275516</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002365338696687945</v>
+        <v>0.002384529579241809</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8195,25 +8195,25 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08375853066839459</v>
+        <v>0.04276213165574472</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1529671327592744</v>
+        <v>0.1027103605825758</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.36397608937349</v>
+        <v>4.360056444564394</v>
       </c>
       <c r="P74" t="n">
-        <v>4.403509512828978</v>
+        <v>4.399168672854175</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9638384190809758</v>
+        <v>0.9638184473111885</v>
       </c>
       <c r="R74" t="n">
-        <v>0.009008222033025953</v>
+        <v>0.009010709275710202</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.7348329767247739</v>
+        <v>0.73597206029267</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.01230276359784669</v>
+        <v>0.01227631054922211</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8090122836622878</v>
+        <v>0.8090452790809056</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001452279341454517</v>
+        <v>0.00145215388669872</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8774164594341005</v>
+        <v>0.8767545637869347</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01378642710674003</v>
+        <v>0.01382359722772736</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8581244659164741</v>
+        <v>0.8586449907352888</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007615859915312293</v>
+        <v>0.007601876220340044</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.6981017776391559</v>
+        <v>0.6937110684949236</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002050931235375082</v>
+        <v>0.002065791437064751</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8299,25 +8299,25 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2067664206129807</v>
+        <v>0.1476874036969633</v>
       </c>
       <c r="L75" t="n">
-        <v>0.262466612229401</v>
+        <v>0.2169565893985138</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.184661703848845</v>
+        <v>4.171047640784607</v>
       </c>
       <c r="P75" t="n">
-        <v>4.290524214380456</v>
+        <v>4.27776692109342</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9659636846522492</v>
+        <v>0.9657094801921927</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007285940917589359</v>
+        <v>0.007313098283009578</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8759969434664582</v>
+        <v>0.8740208605203026</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01258311002769126</v>
+        <v>0.01268297446330159</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8902524808209079</v>
+        <v>0.8961351021145678</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.001998932624330572</v>
+        <v>0.001944622020939978</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9205078240962039</v>
+        <v>0.9207574982133554</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007399706479654176</v>
+        <v>0.007388076588878078</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8684768007298713</v>
+        <v>0.8690569888553221</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006879180253910074</v>
+        <v>0.006863990437626799</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9731388809329852</v>
+        <v>0.9717082228121103</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.001007724524160602</v>
+        <v>0.001034212759901399</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8403,25 +8403,25 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02041481449548191</v>
+        <v>0.006316940755609539</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02255884293081964</v>
+        <v>0.008483195956739714</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.335730785167194</v>
+        <v>4.333353832661424</v>
       </c>
       <c r="P76" t="n">
-        <v>4.319293977451697</v>
+        <v>4.317479738210782</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9927416500394189</v>
+        <v>0.9927448376683182</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005346002972920062</v>
+        <v>0.005344828949501011</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9145185545879547</v>
+        <v>0.9145350171802397</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.008318341052496479</v>
+        <v>0.008317540008492105</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8607171015896948</v>
+        <v>0.8585739604767713</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.001028950544056184</v>
+        <v>0.00103683653759705</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.960457066720408</v>
+        <v>0.9604966151999113</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008394502949186979</v>
+        <v>0.008390304061723348</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9889502385778371</v>
+        <v>0.9889747022648212</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.000883475392491625</v>
+        <v>0.0008824968633347237</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5697404228527605</v>
+        <v>0.5677432836386962</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001181944715941405</v>
+        <v>0.00118468465702498</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8507,25 +8507,25 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0375161600995857</v>
+        <v>0.01454057165154276</v>
       </c>
       <c r="L77" t="n">
-        <v>0.09109877828007409</v>
+        <v>0.05122403444386606</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.235925950677315</v>
+        <v>4.230706129780605</v>
       </c>
       <c r="P77" t="n">
-        <v>4.251805020139015</v>
+        <v>4.241947034272846</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9766838123591988</v>
+        <v>0.9765547341113235</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009156654275950997</v>
+        <v>0.009181964882248461</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.8064700717880768</v>
+        <v>0.8008825463781881</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.008015015453292237</v>
+        <v>0.008129895462709917</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.1097340222524199</v>
+        <v>-0.1437545263104247</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.001030183666321997</v>
+        <v>0.001045855349798166</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.909900377340481</v>
+        <v>0.9094863392615129</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01301219123951124</v>
+        <v>0.01304205467436324</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1750922767891173</v>
+        <v>0.1767500509297294</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01356337782371721</v>
+        <v>0.01354974219022352</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8758796496595981</v>
+        <v>0.8709770043634458</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007984345314874358</v>
+        <v>0.0008140505489980063</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8611,25 +8611,25 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02699802811307632</v>
+        <v>0.009175722573668135</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0790397260377876</v>
+        <v>0.0434006717643905</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.377810298060794</v>
+        <v>4.366330804420246</v>
       </c>
       <c r="P78" t="n">
-        <v>4.386222610833368</v>
+        <v>4.369091597845138</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9783904451258419</v>
+        <v>0.976505735020505</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01067467895894601</v>
+        <v>0.01113045308144458</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.3697360126165589</v>
+        <v>0.3648787444450826</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.009624086527390198</v>
+        <v>0.00966110042728385</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.6906053367269736</v>
+        <v>-0.116363388864779</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006506138719584699</v>
+        <v>0.0012358612130382</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8028645969740215</v>
+        <v>0.7753201191242427</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01825902039580381</v>
+        <v>0.01949293587523502</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2376474446796117</v>
+        <v>-0.2445075441732114</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01172023785490019</v>
+        <v>0.01175267481334801</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.725642576437441</v>
+        <v>-1.968350770628193</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.002437562982966849</v>
+        <v>0.002543776775369619</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8709,31 +8709,31 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2887378674060793</v>
+        <v>0.2286775418539777</v>
       </c>
       <c r="L79" t="n">
-        <v>0.2896789461350093</v>
+        <v>0.2477973577987656</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.358789254115512</v>
+        <v>4.343239893866217</v>
       </c>
       <c r="P79" t="n">
-        <v>4.385411218924689</v>
+        <v>4.418763722425201</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9805398779262914</v>
+        <v>0.9802822522567252</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02052028378665912</v>
+        <v>0.02065566757304671</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9163432795460734</v>
+        <v>0.9151814189038131</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04492521984156974</v>
+        <v>0.04523611452595071</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3459237322995101</v>
+        <v>0.2591224603487993</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002276161351722865</v>
+        <v>0.002422490394025607</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9871635279861676</v>
+        <v>0.9889598183467836</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.008854450549396849</v>
+        <v>0.008211583007147775</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5593185193344927</v>
+        <v>0.4644157139719021</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.005017324186440493</v>
+        <v>0.00553125494608748</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9862256853627619</v>
+        <v>0.9860412998170944</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003765559012547529</v>
+        <v>0.003790678469321131</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8740234792776144</v>
+        <v>0.8660455290081124</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009484654546243096</v>
+        <v>0.009780370768080537</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8817,31 +8817,31 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1595546616330362</v>
+        <v>0.1016449187314903</v>
       </c>
       <c r="L80" t="n">
-        <v>0.1840450935700307</v>
+        <v>0.1456375464187621</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.445589425954382</v>
+        <v>4.435466917526268</v>
       </c>
       <c r="P80" t="n">
-        <v>4.446009014318028</v>
+        <v>4.443679925310524</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9932731795314036</v>
+        <v>0.9929693903336341</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0113361393854839</v>
+        <v>0.011589287912827</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9788754491318208</v>
+        <v>0.9775091588191702</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02308012349968894</v>
+        <v>0.02381481629174361</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7019987906301915</v>
+        <v>0.6462042004879114</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001460232355615892</v>
+        <v>0.001591070011224633</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9831208631198295</v>
+        <v>0.9855312479033738</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.008341334461357996</v>
+        <v>0.007722820755760248</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.7232724348419159</v>
+        <v>0.6670547754035783</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.004376921555140897</v>
+        <v>0.004800969503416321</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9827151395388187</v>
+        <v>0.9833752270534847</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.006973447969835452</v>
+        <v>0.006838998180972959</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9726013777166624</v>
+        <v>0.970683631907028</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.005422878523955323</v>
+        <v>0.005609454065794333</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8925,31 +8925,31 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2672160292479843</v>
+        <v>0.218460323060076</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2461893094758684</v>
+        <v>0.2075952207838404</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.565126561556436</v>
+        <v>4.558610219689993</v>
       </c>
       <c r="P81" t="n">
-        <v>4.554905759427732</v>
+        <v>4.543399396161489</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9907375823719937</v>
+        <v>0.9911124672284075</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01307912088022594</v>
+        <v>0.01281170652572323</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9730374839034356</v>
+        <v>0.9743457858163478</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02460751024770663</v>
+        <v>0.02400307179224516</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9735865702716282</v>
+        <v>0.974302237947929</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.01071120845530277</v>
+        <v>0.01056510273852949</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.8122120651235197</v>
+        <v>0.7063361793108001</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.002631412180757075</v>
+        <v>0.003290639148177881</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9671114570058318</v>
+        <v>0.9686427629428078</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005818153245732371</v>
+        <v>0.005681090842897096</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9599325355082032</v>
+        <v>0.9618258188562443</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009709903736804569</v>
+        <v>0.009477719662353761</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9029,31 +9029,31 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1476585777734352</v>
+        <v>0.1388222346861923</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1779486003915289</v>
+        <v>0.149433185371118</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.56381144856591</v>
+        <v>4.55959061557802</v>
       </c>
       <c r="P82" t="n">
-        <v>4.581373345847023</v>
+        <v>4.561536607591272</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9634987131821567</v>
+        <v>0.9630795473073034</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02577265442699048</v>
+        <v>0.02592021333048817</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.8986288775067877</v>
+        <v>0.8969148330458542</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04970877636834458</v>
+        <v>0.0501272678362678</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.8959236790392618</v>
+        <v>0.89531049721977</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.02160123669770234</v>
+        <v>0.02166477677756945</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>-0.1560668513950476</v>
+        <v>0.1303848286175314</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.003155700205137652</v>
+        <v>0.002736956013090728</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7610768122425228</v>
+        <v>0.7626797781202245</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01758526539184303</v>
+        <v>0.01752617520537911</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9769425019968285</v>
+        <v>0.9776046786213118</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.00802326015226024</v>
+        <v>0.007907212934530202</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9133,29 +9133,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1893204027356125</v>
+        <v>0.1276873733991883</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1634266058404603</v>
+        <v>0.1239523889080047</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.564646219566645</v>
+        <v>4.58025111211242</v>
       </c>
       <c r="P83" t="n">
-        <v>4.536174058062235</v>
+        <v>4.567790528926106</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9761844962819626</v>
+        <v>0.9754756867524184</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01847620034728505</v>
+        <v>0.0187491336190449</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9265243363566215</v>
+        <v>0.9239786067899424</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03513016145849297</v>
+        <v>0.03573356114189276</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9586179704669509</v>
+        <v>0.9584923919564921</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009809389446916533</v>
+        <v>0.009824262005543543</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2944383579636647</v>
+        <v>0.226683993556182</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009388122675349825</v>
+        <v>0.009828557584918914</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9234468865166462</v>
+        <v>0.9224379080909332</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01062119376946844</v>
+        <v>0.01069095885219543</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.873688303543886</v>
+        <v>0.8752723366711107</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01324956325650039</v>
+        <v>0.01316622178567719</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9235,29 +9235,29 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.168261400395764</v>
+        <v>0.08086517134350701</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2392951190050516</v>
+        <v>0.2377556632155571</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.508063070964528</v>
+        <v>3.412699872579033</v>
       </c>
       <c r="P84" t="n">
-        <v>4.520851279602867</v>
+        <v>4.455310795137662</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9947306388470482</v>
+        <v>0.9870028127100727</v>
       </c>
       <c r="R84" t="n">
-        <v>0.008524515940662752</v>
+        <v>0.01338799167725814</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9927419426496462</v>
+        <v>0.9785203180521072</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01139444999852478</v>
+        <v>0.01960185139532164</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9940969056185013</v>
+        <v>0.9858700785127035</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.005241691383021949</v>
+        <v>0.00810963782196405</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.2590606781900662</v>
+        <v>0.0429963999184364</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.007793164024025685</v>
+        <v>0.008856850967128812</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9172944531408367</v>
+        <v>0.7850024112685011</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01185248531875967</v>
+        <v>0.01910992153241521</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9953609395978528</v>
+        <v>0.9975327378031454</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002193906801246853</v>
+        <v>0.001599966248071254</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9337,29 +9337,31 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.232384799749474</v>
+        <v>0.2341581070084072</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2782905441772863</v>
+        <v>0.2186140151402936</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9370,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.4579287131415</v>
+        <v>4.338754752871146</v>
       </c>
       <c r="P85" t="n">
-        <v>4.497065890760551</v>
+        <v>4.379848319544478</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9805986405922199</v>
+        <v>0.9933764004370673</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01740773827383034</v>
+        <v>0.01029566010579224</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9491154746544618</v>
+        <v>0.9791978758746076</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02895977228546437</v>
+        <v>0.0203558127954359</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9943039542316575</v>
+        <v>0.9971716392463389</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.005816080150991643</v>
+        <v>0.004325589007609165</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.1927799087396398</v>
+        <v>0.4883486112021659</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01706662279498498</v>
+        <v>0.005697062005441004</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.6634729868567384</v>
+        <v>0.9521753106124168</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.01873650625006663</v>
+        <v>0.006725299455058912</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9996007539848109</v>
+        <v>0.9705323657719575</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.0005703330755728907</v>
+        <v>0.004387149643033924</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9439,29 +9441,31 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1217276426814131</v>
+        <v>0.1048616667183305</v>
       </c>
       <c r="L86" t="n">
-        <v>0.548252343981105</v>
+        <v>0.1406074899570365</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9474,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.465527496290664</v>
+        <v>4.45685408733002</v>
       </c>
       <c r="P86" t="n">
-        <v>4.581111611572777</v>
+        <v>4.45061676110979</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.8814029662123379</v>
+        <v>0.9911588201859275</v>
       </c>
       <c r="R86" t="n">
-        <v>0.04107313565112523</v>
+        <v>0.01169520775248249</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.8100861392994358</v>
+        <v>0.9774908683288092</v>
       </c>
       <c r="U86" t="n">
-        <v>0.06057562069434851</v>
+        <v>0.02333294882216887</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9962561741154657</v>
+        <v>0.9924748277980114</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003559144394161952</v>
+        <v>0.005516741901278098</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>0.5784462124008252</v>
+        <v>0.6152286426970714</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.009718601274682612</v>
+        <v>0.005213909775754872</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>-0.7682385120692303</v>
+        <v>0.973422203263863</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.06798514155595548</v>
+        <v>0.008522588139415204</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9654345316830725</v>
+        <v>0.991523252370911</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.006042213719740869</v>
+        <v>0.003034652563564792</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9541,29 +9545,31 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836792919038959</v>
+        <v>0.1625122195698727</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2897898832411685</v>
+        <v>0.1594955276605785</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9578,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.626284423183901</v>
+        <v>4.559708044000981</v>
       </c>
       <c r="P87" t="n">
-        <v>4.640097022354929</v>
+        <v>4.552023058625678</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9575810697455271</v>
+        <v>0.9600647074275883</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02308916945910394</v>
+        <v>0.02672382211234957</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9137800842870558</v>
+        <v>0.9010662748015633</v>
       </c>
       <c r="U87" t="n">
-        <v>0.03807360341033582</v>
+        <v>0.05188283031963875</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.9044295049137443</v>
+        <v>0.9046319179400172</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.01727832412035614</v>
+        <v>0.0211828004966979</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.6318813551480504</v>
+        <v>0.3734747550435138</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.007111819540295957</v>
+        <v>0.003096546453005686</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.333906347676852</v>
+        <v>0.7818291228846775</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.02883609532154794</v>
+        <v>0.0186652452595633</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.986049614531881</v>
+        <v>0.9757492234338004</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.005942272287041352</v>
+        <v>0.008502602076300917</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9643,29 +9649,31 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2310798297965026</v>
+        <v>0.2203248872293976</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1753763876980404</v>
+        <v>0.2157298215422599</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9682,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.585737126599059</v>
+        <v>4.564397093213429</v>
       </c>
       <c r="P88" t="n">
-        <v>4.622357867172565</v>
+        <v>4.544196781972164</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9875930915909575</v>
+        <v>0.9881137798927422</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01305934674979869</v>
+        <v>0.01466774448721427</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9628607252871669</v>
+        <v>0.9680639793703214</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02428913380964197</v>
+        <v>0.02776683559159969</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9665714674301151</v>
+        <v>0.9680937205853716</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.01034480261303945</v>
+        <v>0.0121506568761078</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5292271408097087</v>
+        <v>0.825034825247103</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004279956530047157</v>
+        <v>0.002563774592715642</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9663906243619471</v>
+        <v>0.9673868010330234</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.005464361768466608</v>
+        <v>0.005907981370274018</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9481456890308845</v>
+        <v>0.9550639432276308</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01037200308022392</v>
+        <v>0.01075178293983981</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9745,29 +9753,29 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3391853656933783</v>
+        <v>0.2930745491696932</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3168741071271186</v>
+        <v>0.2726888545910091</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9784,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.50704372858565</v>
+        <v>4.501956059923095</v>
       </c>
       <c r="P89" t="n">
-        <v>4.604623003407573</v>
+        <v>4.556115097233604</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9950787838142697</v>
+        <v>0.9932580111502747</v>
       </c>
       <c r="R89" t="n">
-        <v>0.008301702887742093</v>
+        <v>0.009716838390799292</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9928338874139709</v>
+        <v>0.9861352504462411</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01156869286342268</v>
+        <v>0.01609157271916382</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9917894683747683</v>
+        <v>0.9937761285784626</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.006905325378730429</v>
+        <v>0.006012136252425829</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7712477100601002</v>
+        <v>0.6513168201240858</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004635085658713924</v>
+        <v>0.005722561882954829</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9828675022844365</v>
+        <v>0.973080694007983</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.003180108932496803</v>
+        <v>0.003986241320865744</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9365111335651226</v>
+        <v>0.9380146967130912</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01146630145867534</v>
+        <v>0.0113297136900391</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9849,27 +9857,29 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.226725035550164</v>
+        <v>0.4648934235510218</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4805611621302232</v>
+        <v>0.5368776908003706</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9888,56 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.483427880631227</v>
+        <v>4.563095274616819</v>
       </c>
       <c r="P90" t="n">
-        <v>4.282245688652591</v>
+        <v>4.29881684734502</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.985456612282216</v>
+        <v>0.984141649636149</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01594676443091195</v>
+        <v>0.01495162684796266</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.968770809940952</v>
+        <v>0.964786523779473</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02861977711843928</v>
+        <v>0.0273297299993891</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5.204170427930421e-18</v>
+      </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9922180759568158</v>
+        <v>0.9900309772756302</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01139589804942022</v>
+        <v>0.01085023216418148</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.7980355159901387</v>
+        <v>0.8676335937391711</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.005120169371456811</v>
+        <v>0.005656931144850531</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9878729345013798</v>
+        <v>0.9480030107558425</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.000838779863944477</v>
+        <v>0.0007528076882725982</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9876930109154459</v>
+        <v>0.9844037445949971</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003636273520163143</v>
+        <v>0.003840930341092464</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
